--- a/docs/harness/wirelist/B-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/B-cabin-wirelist.xlsx
@@ -1222,7 +1222,7 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>DRB102 76 = section B c12 'Back-up switch B1 pin 1 out (+12V in reverse) -&gt; r'; splice sp_rev_sw named in SoT</t>
+          <t>DRB102 76 = section B c12 'Back-up switch B1 pin 1 out (+12V in reverse) -&gt; r'; splice sp_rev_sw: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
@@ -1337,7 +1337,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>DRB102 84 = section B c17 'Knock 1 SIG- (to Gnd Out B22)'; splice sp_gnd_bhb named in SoT</t>
+          <t>DRB102 84 = section B c17 'Knock 1 SIG- (to Gnd Out B22)'; splice sp_gnd_bhb: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1452,7 +1452,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>DRB102 85 = section B c18 'Knock 1 screen'; splice sp_shield_b named in SoT</t>
+          <t>DRB102 85 = section B c18 'Knock 1 screen'; splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1567,7 +1567,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>DRB102 88 = section B c22 'ETB motor screen (to B17)'; splice sp_shield_b named in SoT</t>
+          <t>DRB102 88 = section B c22 'ETB motor screen (to B17)'; splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
@@ -1795,7 +1795,7 @@
       <c r="AD8" s="54" t="inlineStr"/>
       <c r="AE8" s="54" t="inlineStr">
         <is>
-          <t>DRB102 91 = section B c23 'Gearbox VSS screen (to B17)'; splice sp_shield_b named in SoT</t>
+          <t>DRB102 91 = section B c23 'Gearbox VSS screen (to B17)'; splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF8" s="54" t="inlineStr">
@@ -2830,7 +2830,7 @@
       <c r="AD17" s="38" t="inlineStr"/>
       <c r="AE17" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B22 Gnd Out (GNDOUT); splice sp_gndout_b named in SoT</t>
+          <t>channels.csv ecu_b B22 Gnd Out (GNDOUT_B); splice sp_gndout_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF17" s="38" t="inlineStr">
@@ -3169,12 +3169,12 @@
       <c r="AD20" s="54" t="inlineStr"/>
       <c r="AE20" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B31 An Volt 10 (AV10_AC_BTN)</t>
+          <t>channels.csv ecu_b B31 An Volt 10 (AV10_AC_BTN); splice sp_ac_btn: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF20" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_ac_btn is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG20" s="54" t="inlineStr"/>
@@ -3282,12 +3282,12 @@
       <c r="AD21" s="38" t="inlineStr"/>
       <c r="AE21" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B32 An Volt 11 (AV11_EVAP_TEMP)</t>
+          <t>channels.csv ecu_b B32 An Volt 11 (AV11_EVAP_TEMP); splice sp_evap: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF21" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_evap is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG21" s="38" t="inlineStr"/>
@@ -3514,10 +3514,14 @@
       <c r="AB23" s="37" t="inlineStr"/>
       <c r="AC23" s="38" t="inlineStr"/>
       <c r="AD23" s="38" t="inlineStr"/>
-      <c r="AE23" s="38" t="inlineStr"/>
+      <c r="AE23" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_fl_sig: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF23" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_fl_sig is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG23" s="38" t="inlineStr"/>
@@ -3627,7 +3631,7 @@
       <c r="AD24" s="54" t="inlineStr"/>
       <c r="AE24" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b named in SoT</t>
+          <t>splice sp_gndout_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF24" s="54" t="inlineStr">
@@ -3875,7 +3879,7 @@
       <c r="AD26" s="54" t="inlineStr"/>
       <c r="AE26" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v_b named in SoT</t>
+          <t>splice sp_5v_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF26" s="54" t="inlineStr">
@@ -3990,7 +3994,7 @@
       <c r="AD27" s="38" t="inlineStr"/>
       <c r="AE27" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b named in SoT</t>
+          <t>splice sp_gndout_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF27" s="38" t="inlineStr">
@@ -4337,7 +4341,7 @@
       <c r="AD30" s="54" t="inlineStr"/>
       <c r="AE30" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_b named in SoT</t>
+          <t>splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF30" s="54" t="inlineStr">
@@ -4696,10 +4700,14 @@
       <c r="AB33" s="37" t="inlineStr"/>
       <c r="AC33" s="38" t="inlineStr"/>
       <c r="AD33" s="38" t="inlineStr"/>
-      <c r="AE33" s="38" t="inlineStr"/>
+      <c r="AE33" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_ac_btn: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF33" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_ac_btn is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG33" s="38" t="inlineStr"/>
@@ -4809,7 +4817,7 @@
       <c r="AD34" s="54" t="inlineStr"/>
       <c r="AE34" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b named in SoT</t>
+          <t>splice sp_gndout_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF34" s="54" t="inlineStr">
@@ -4920,7 +4928,7 @@
       <c r="AD35" s="38" t="inlineStr"/>
       <c r="AE35" s="38" t="inlineStr">
         <is>
-          <t>splice sp_5v_b named in SoT</t>
+          <t>splice sp_5v_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF35" s="38" t="inlineStr">
@@ -5031,7 +5039,7 @@
       <c r="AD36" s="54" t="inlineStr"/>
       <c r="AE36" s="54" t="inlineStr">
         <is>
-          <t>splice sp_5v_b named in SoT</t>
+          <t>splice sp_5v_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF36" s="54" t="inlineStr">
@@ -5140,10 +5148,14 @@
       <c r="AB37" s="37" t="inlineStr"/>
       <c r="AC37" s="38" t="inlineStr"/>
       <c r="AD37" s="38" t="inlineStr"/>
-      <c r="AE37" s="38" t="inlineStr"/>
+      <c r="AE37" s="38" t="inlineStr">
+        <is>
+          <t>splice sp_ac_btn: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF37" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_ac_btn is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG37" s="38" t="inlineStr"/>
@@ -5259,12 +5271,12 @@
       <c r="AD38" s="54" t="inlineStr"/>
       <c r="AE38" s="54" t="inlineStr">
         <is>
-          <t>DRB102 92 = section B c13 'CAN H to Link CAN-Lambda (ST185-CAN)'</t>
+          <t>splice sp_canh: node of the wire list (SoT); DRB102 92 = section B c13 'CAN H to Link CAN-Lambda (ST185-CAN)'</t>
         </is>
       </c>
       <c r="AF38" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canh is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG38" s="54" t="inlineStr">
@@ -5384,12 +5396,12 @@
       <c r="AD39" s="38" t="inlineStr"/>
       <c r="AE39" s="38" t="inlineStr">
         <is>
-          <t>DRB102 93 = section B c14 'CAN L to Link CAN-Lambda (ST185-CAN)'</t>
+          <t>splice sp_canl: node of the wire list (SoT); DRB102 93 = section B c14 'CAN L to Link CAN-Lambda (ST185-CAN)'</t>
         </is>
       </c>
       <c r="AF39" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_canl is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG39" s="38" t="inlineStr">
@@ -5497,10 +5509,14 @@
       <c r="AB40" s="53" t="inlineStr"/>
       <c r="AC40" s="54" t="inlineStr"/>
       <c r="AD40" s="54" t="inlineStr"/>
-      <c r="AE40" s="54" t="inlineStr"/>
+      <c r="AE40" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_evap: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF40" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_evap is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG40" s="54" t="inlineStr"/>
@@ -5608,12 +5624,12 @@
       <c r="AD41" s="38" t="inlineStr"/>
       <c r="AE41" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B24 An Volt 9 (AV9_FUEL_LVL)</t>
+          <t>splice sp_fl_sig: node of the wire list (SoT); channels.csv ecu_b B24 An Volt 9 (AV9_FUEL_LVL)</t>
         </is>
       </c>
       <c r="AF41" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_fl_sig is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG41" s="38" t="inlineStr"/>
@@ -5717,10 +5733,14 @@
       <c r="AB42" s="53" t="inlineStr"/>
       <c r="AC42" s="54" t="inlineStr"/>
       <c r="AD42" s="54" t="inlineStr"/>
-      <c r="AE42" s="54" t="inlineStr"/>
+      <c r="AE42" s="54" t="inlineStr">
+        <is>
+          <t>splice sp_fl_sig: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF42" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_fl_sig is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG42" s="54" t="inlineStr"/>
@@ -5830,7 +5850,7 @@
       <c r="AD43" s="38" t="inlineStr"/>
       <c r="AE43" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb named in SoT; DRB102 77 = section B c19 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
+          <t>splice sp_gnd_bhb: node of the wire list (SoT); DRB102 77 = section B c19 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
         </is>
       </c>
       <c r="AF43" s="38" t="inlineStr">
@@ -5945,7 +5965,7 @@
       <c r="AD44" s="54" t="inlineStr"/>
       <c r="AE44" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb named in SoT; DRB102 78 = section B c21 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
+          <t>splice sp_gnd_bhb: node of the wire list (SoT); DRB102 78 = section B c21 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
         </is>
       </c>
       <c r="AF44" s="54" t="inlineStr">
@@ -6058,7 +6078,7 @@
       <c r="AD45" s="38" t="inlineStr"/>
       <c r="AE45" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b named in SoT; splice sp_gnd_bhb named in SoT</t>
+          <t>splice sp_gndout_b: node of the wire list (SoT); splice sp_gnd_bhb: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF45" s="38" t="inlineStr">
@@ -6179,12 +6199,12 @@
       <c r="AD46" s="54" t="inlineStr"/>
       <c r="AE46" s="54" t="inlineStr">
         <is>
-          <t>DRB102 62 = section B c25 'Back-up switch B1 pin 2 feed &lt;- J/B No.1 GAUGE 15A'</t>
+          <t>splice sp_rev_gauge: node of the wire list (SoT); DRB102 62 = section B c25 'Back-up switch B1 pin 2 feed &lt;- J/B No.1 GAUGE 15A'</t>
         </is>
       </c>
       <c r="AF46" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: splice sp_rev_gauge is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG46" s="54" t="inlineStr">
@@ -6302,7 +6322,7 @@
       <c r="AD47" s="38" t="inlineStr"/>
       <c r="AE47" s="38" t="inlineStr">
         <is>
-          <t>splice sp_rev_sw named in SoT; channels.csv k_rev c3 Coil 86 (REV_SW); fuse-box plan k_rev 86 (16 AWG)</t>
+          <t>splice sp_rev_sw: node of the wire list (SoT); channels.csv k_rev c3 Coil 86 (REV_SW); fuse-box plan k_rev 86 (16 AWG)</t>
         </is>
       </c>
       <c r="AF47" s="38" t="inlineStr">
@@ -6427,7 +6447,7 @@
       <c r="AD48" s="54" t="inlineStr"/>
       <c r="AE48" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rev_sw named in SoT</t>
+          <t>splice sp_rev_sw: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF48" s="54" t="inlineStr">
@@ -6548,7 +6568,7 @@
       <c r="AD49" s="38" t="inlineStr"/>
       <c r="AE49" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_b named in SoT; channels.csv ecu_b B17 Shield/Gnd (SHIELD_B)</t>
+          <t>splice sp_shield_b: node of the wire list (SoT); channels.csv ecu_b B17 Shield/Gnd (SHIELD_B)</t>
         </is>
       </c>
       <c r="AF49" s="38" t="inlineStr">
@@ -6667,7 +6687,7 @@
       <c r="AD50" s="54" t="inlineStr"/>
       <c r="AE50" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_can named in SoT; DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to B17, via the CAN sc'</t>
+          <t>splice sp_shield_can: node of the wire list (SoT); DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to B17, via the CAN sc'</t>
         </is>
       </c>
       <c r="AF50" s="54" t="inlineStr">
@@ -6788,7 +6808,7 @@
       <c r="AD51" s="38" t="inlineStr"/>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_can named in SoT; splice sp_shield_b named in SoT</t>
+          <t>splice sp_shield_can: node of the wire list (SoT); splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -6897,10 +6917,14 @@
       <c r="AB52" s="53" t="inlineStr"/>
       <c r="AC52" s="54" t="inlineStr"/>
       <c r="AD52" s="54" t="inlineStr"/>
-      <c r="AE52" s="54" t="inlineStr"/>
+      <c r="AE52" s="54" t="inlineStr">
+        <is>
+          <t>end t_ac_btn: end row of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF52" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_ac_btn (OEM dash A/C switch V-G lead (old A15 pin 3)) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG52" s="54" t="inlineStr"/>
@@ -7008,12 +7032,12 @@
       <c r="AD53" s="38" t="inlineStr"/>
       <c r="AE53" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b named in SoT</t>
+          <t>end t_evap_rtn: end row of the wire list (SoT); splice sp_gndout_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF53" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_evap_rtn (OEM evaporator thermistor A24 pin 2, at the evap case) is drawing-only: not named in the SoT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG53" s="38" t="inlineStr"/>
@@ -7115,10 +7139,14 @@
       <c r="AB54" s="53" t="inlineStr"/>
       <c r="AC54" s="54" t="inlineStr"/>
       <c r="AD54" s="54" t="inlineStr"/>
-      <c r="AE54" s="54" t="inlineStr"/>
+      <c r="AE54" s="54" t="inlineStr">
+        <is>
+          <t>end t_evap_temp: end row of the wire list (SoT); splice sp_evap: node of the wire list (SoT)</t>
+        </is>
+      </c>
       <c r="AF54" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: end t_evap_temp (OEM evaporator thermistor A24 pin 1, at the evap case) is drawing-only: not named in the SoT; splice sp_evap is not named in the SoT (drawing only)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="AG54" s="54" t="inlineStr"/>
@@ -10085,7 +10113,7 @@
       </c>
       <c r="L3" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10169,7 @@
       </c>
       <c r="L4" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10197,7 +10225,7 @@
       </c>
       <c r="L5" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10281,7 @@
       </c>
       <c r="L6" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10309,7 +10337,7 @@
       </c>
       <c r="L7" s="38" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10393,7 @@
       </c>
       <c r="L8" s="54" t="inlineStr">
         <is>
-          <t>named in SoT</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10449,7 @@
       </c>
       <c r="L9" s="38" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>
@@ -10477,7 +10505,7 @@
       </c>
       <c r="L10" s="54" t="inlineStr">
         <is>
-          <t>SOT GAP: not named in the SoT (drawing only)</t>
+          <t>node of the wire list (SoT)</t>
         </is>
       </c>
     </row>

--- a/docs/harness/wirelist/B-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/B-cabin-wirelist.xlsx
@@ -3372,7 +3372,7 @@
       </c>
       <c r="R22" s="47" t="inlineStr">
         <is>
-          <t>+12V B30 2A (LOGIC BUS2-13)</t>
+          <t>+12V Start request (LOGIC BUS2-13)</t>
         </is>
       </c>
       <c r="S22" s="48" t="inlineStr"/>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="I25" s="59" t="inlineStr">
         <is>
-          <t>+12V LAM 7.5A (LOGIC BUS2-1)</t>
+          <t>+12V CAN-Lambda +12 V (LOGIC BUS2-1)</t>
         </is>
       </c>
       <c r="J25" s="60" t="inlineStr">

--- a/docs/harness/wirelist/B-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/B-cabin-wirelist.xlsx
@@ -6396,7 +6396,7 @@
       </c>
       <c r="N48" s="44" t="inlineStr">
         <is>
-          <t>i2</t>
+          <t>IN2</t>
         </is>
       </c>
       <c r="O48" s="45" t="inlineStr">

--- a/docs/harness/wirelist/B-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/B-cabin-wirelist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG92"/>
+  <dimension ref="A1:AG91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
     <col width="36" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
@@ -6606,12 +6606,12 @@
       </c>
       <c r="F50" s="41" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_can_sh_bh</t>
         </is>
       </c>
       <c r="G50" s="42" t="inlineStr">
         <is>
-          <t>splice sp_shield_can (CAN screen join)</t>
+          <t>splice sp_can_sh_bh (SP-CAN-SH-BH)</t>
         </is>
       </c>
       <c r="H50" s="41" t="inlineStr"/>
@@ -6647,17 +6647,17 @@
       <c r="P50" s="45" t="inlineStr"/>
       <c r="Q50" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R50" s="47" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="S50" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>sp_can_sh_bh</t>
         </is>
       </c>
       <c r="T50" s="48" t="inlineStr">
@@ -6687,7 +6687,7 @@
       <c r="AD50" s="54" t="inlineStr"/>
       <c r="AE50" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_can: node of the wire list (SoT); DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to B17, via the CAN sc'</t>
+          <t>splice sp_can_sh_bh: node of the wire list (SoT); DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to ECU C1, via the CAN'</t>
         </is>
       </c>
       <c r="AF50" s="54" t="inlineStr">
@@ -6704,12 +6704,12 @@
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>ACBTN</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>w_shd_can_bc</t>
+          <t>w_ac_btn_in</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
@@ -6717,87 +6717,77 @@
           <t>B-cabin</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
+      <c r="D51" s="23" t="inlineStr"/>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>sp_shield_can</t>
+          <t>t_ac_btn</t>
         </is>
       </c>
       <c r="G51" s="26" t="inlineStr">
         <is>
-          <t>splice sp_shield_can (CAN screen join)</t>
+          <t>OEM dash A/C switch V-G lead (old A15 pin 3)</t>
         </is>
       </c>
       <c r="H51" s="25" t="inlineStr"/>
       <c r="I51" s="26" t="inlineStr">
         <is>
-          <t>CAN shields to B17</t>
+          <t>A/C switch V-G in</t>
         </is>
       </c>
       <c r="J51" s="26" t="inlineStr"/>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>resistor</t>
         </is>
       </c>
       <c r="L51" s="28" t="inlineStr">
         <is>
-          <t>sp_shield_b</t>
+          <t>r_ac_btn_hi</t>
         </is>
       </c>
       <c r="M51" s="29" t="inlineStr">
         <is>
-          <t>splice sp_shield_b (SP-SHIELD-B)</t>
-        </is>
-      </c>
-      <c r="N51" s="28" t="inlineStr"/>
+          <t>10k A/C switch divider, top</t>
+        </is>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>1</v>
+      </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
-          <t>CAN shields to B17</t>
+          <t>A/C switch V-G in</t>
         </is>
       </c>
       <c r="P51" s="29" t="inlineStr"/>
       <c r="Q51" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B17</t>
+          <t>r_ac_btn_hi.1</t>
         </is>
       </c>
       <c r="R51" s="31" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
-        </is>
-      </c>
-      <c r="S51" s="32" t="inlineStr">
-        <is>
-          <t>sp_shield_can</t>
-        </is>
-      </c>
+          <t>A/C switch V-G in (r_ac_btn_hi 1)</t>
+        </is>
+      </c>
+      <c r="S51" s="32" t="inlineStr"/>
       <c r="T51" s="32" t="inlineStr"/>
       <c r="U51" s="33" t="n">
         <v>20</v>
       </c>
       <c r="V51" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W51" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="W51" s="34" t="inlineStr"/>
       <c r="X51" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="Y51" s="34" t="inlineStr"/>
@@ -6808,7 +6798,7 @@
       <c r="AD51" s="38" t="inlineStr"/>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>splice sp_shield_can: node of the wire list (SoT); splice sp_shield_b: node of the wire list (SoT)</t>
+          <t>end t_ac_btn: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -6816,21 +6806,17 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG51" s="38" t="inlineStr">
-        <is>
-          <t>owner TBD: a half has no length estimate (drawn today as w_shd_can on CAN, ? mm; w_shd_can_bc on B-cabin, ? mm)</t>
-        </is>
-      </c>
+      <c r="AG51" s="38" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>ACBTN</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>w_ac_btn_in</t>
+          <t>w_evap_rtn</t>
         </is>
       </c>
       <c r="C52" s="39" t="inlineStr">
@@ -6846,69 +6832,75 @@
       </c>
       <c r="F52" s="41" t="inlineStr">
         <is>
-          <t>t_ac_btn</t>
+          <t>t_evap_rtn</t>
         </is>
       </c>
       <c r="G52" s="42" t="inlineStr">
         <is>
-          <t>OEM dash A/C switch V-G lead (old A15 pin 3)</t>
+          <t>OEM evaporator thermistor A24 pin 2, at the evap case</t>
         </is>
       </c>
       <c r="H52" s="41" t="inlineStr"/>
       <c r="I52" s="42" t="inlineStr">
         <is>
-          <t>A/C switch V-G in</t>
+          <t>Evap thermistor gnd</t>
         </is>
       </c>
       <c r="J52" s="42" t="inlineStr"/>
       <c r="K52" s="43" t="inlineStr">
         <is>
-          <t>resistor</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L52" s="44" t="inlineStr">
         <is>
-          <t>r_ac_btn_hi</t>
+          <t>sp_gndout_b</t>
         </is>
       </c>
       <c r="M52" s="45" t="inlineStr">
         <is>
-          <t>10k A/C switch divider, top</t>
-        </is>
-      </c>
-      <c r="N52" s="44" t="n">
-        <v>1</v>
-      </c>
+          <t>splice sp_gndout_b (SP-GNDOUT-B)</t>
+        </is>
+      </c>
+      <c r="N52" s="44" t="inlineStr"/>
       <c r="O52" s="45" t="inlineStr">
         <is>
-          <t>A/C switch V-G in</t>
+          <t>Evap thermistor gnd</t>
         </is>
       </c>
       <c r="P52" s="45" t="inlineStr"/>
       <c r="Q52" s="46" t="inlineStr">
         <is>
-          <t>r_ac_btn_hi.1</t>
+          <t>ECU-B.B22</t>
         </is>
       </c>
       <c r="R52" s="47" t="inlineStr">
         <is>
-          <t>A/C switch V-G in (r_ac_btn_hi 1)</t>
-        </is>
-      </c>
-      <c r="S52" s="48" t="inlineStr"/>
+          <t>Sensor GND B (ECU-B B22)</t>
+        </is>
+      </c>
+      <c r="S52" s="48" t="inlineStr">
+        <is>
+          <t>sp_gndout_b</t>
+        </is>
+      </c>
       <c r="T52" s="48" t="inlineStr"/>
       <c r="U52" s="49" t="n">
         <v>20</v>
       </c>
       <c r="V52" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="W52" s="50" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W52" s="50" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
       <c r="X52" s="50" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y52" s="50" t="inlineStr"/>
@@ -6919,7 +6911,7 @@
       <c r="AD52" s="54" t="inlineStr"/>
       <c r="AE52" s="54" t="inlineStr">
         <is>
-          <t>end t_ac_btn: end row of the wire list (SoT)</t>
+          <t>end t_evap_rtn: end row of the wire list (SoT); splice sp_gndout_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF52" s="54" t="inlineStr">
@@ -6932,12 +6924,12 @@
     <row r="53">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>EVAP</t>
         </is>
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>w_evap_rtn</t>
+          <t>w_evap_sig</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
@@ -6953,18 +6945,18 @@
       </c>
       <c r="F53" s="25" t="inlineStr">
         <is>
-          <t>t_evap_rtn</t>
+          <t>t_evap_temp</t>
         </is>
       </c>
       <c r="G53" s="26" t="inlineStr">
         <is>
-          <t>OEM evaporator thermistor A24 pin 2, at the evap case</t>
+          <t>OEM evaporator thermistor A24 pin 1, at the evap case</t>
         </is>
       </c>
       <c r="H53" s="25" t="inlineStr"/>
       <c r="I53" s="26" t="inlineStr">
         <is>
-          <t>Evap thermistor gnd</t>
+          <t>Evap thermistor sig</t>
         </is>
       </c>
       <c r="J53" s="26" t="inlineStr"/>
@@ -6975,34 +6967,34 @@
       </c>
       <c r="L53" s="28" t="inlineStr">
         <is>
-          <t>sp_gndout_b</t>
+          <t>sp_evap</t>
         </is>
       </c>
       <c r="M53" s="29" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b (SP-GNDOUT-B)</t>
+          <t>splice sp_evap (SP-EVAP)</t>
         </is>
       </c>
       <c r="N53" s="28" t="inlineStr"/>
       <c r="O53" s="29" t="inlineStr">
         <is>
-          <t>Evap thermistor gnd</t>
+          <t>Evap thermistor sig</t>
         </is>
       </c>
       <c r="P53" s="29" t="inlineStr"/>
       <c r="Q53" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B22</t>
+          <t>ECU-B.B32</t>
         </is>
       </c>
       <c r="R53" s="31" t="inlineStr">
         <is>
-          <t>Sensor GND B (ECU-B B22)</t>
+          <t>Evap temp signal (ECU-B B32)</t>
         </is>
       </c>
       <c r="S53" s="32" t="inlineStr">
         <is>
-          <t>sp_gndout_b</t>
+          <t>sp_evap</t>
         </is>
       </c>
       <c r="T53" s="32" t="inlineStr"/>
@@ -7011,17 +7003,13 @@
       </c>
       <c r="V53" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W53" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="W53" s="34" t="inlineStr"/>
       <c r="X53" s="34" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
+          <t>Blue-Blue-White</t>
         </is>
       </c>
       <c r="Y53" s="34" t="inlineStr"/>
@@ -7032,7 +7020,7 @@
       <c r="AD53" s="38" t="inlineStr"/>
       <c r="AE53" s="38" t="inlineStr">
         <is>
-          <t>end t_evap_rtn: end row of the wire list (SoT); splice sp_gndout_b: node of the wire list (SoT)</t>
+          <t>end t_evap_temp: end row of the wire list (SoT); splice sp_evap: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF53" s="38" t="inlineStr">
@@ -7043,16 +7031,8 @@
       <c r="AG53" s="38" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr">
-        <is>
-          <t>EVAP</t>
-        </is>
-      </c>
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>w_evap_sig</t>
-        </is>
-      </c>
+      <c r="A54" s="39" t="inlineStr"/>
+      <c r="B54" s="39" t="inlineStr"/>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>B-cabin</t>
@@ -7061,78 +7041,50 @@
       <c r="D54" s="39" t="inlineStr"/>
       <c r="E54" s="40" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="F54" s="41" t="inlineStr">
         <is>
-          <t>t_evap_temp</t>
+          <t>bh_b_fw</t>
         </is>
       </c>
       <c r="G54" s="42" t="inlineStr">
         <is>
-          <t>OEM evaporator thermistor A24 pin 1, at the evap case</t>
-        </is>
-      </c>
-      <c r="H54" s="41" t="inlineStr"/>
+          <t>BH-B (firewall bulkhead DRB102, RH)</t>
+        </is>
+      </c>
+      <c r="H54" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="I54" s="42" t="inlineStr">
         <is>
-          <t>Evap thermistor sig</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J54" s="42" t="inlineStr"/>
-      <c r="K54" s="43" t="inlineStr">
-        <is>
-          <t>splice</t>
-        </is>
-      </c>
-      <c r="L54" s="44" t="inlineStr">
-        <is>
-          <t>sp_evap</t>
-        </is>
-      </c>
-      <c r="M54" s="45" t="inlineStr">
-        <is>
-          <t>splice sp_evap (SP-EVAP)</t>
-        </is>
-      </c>
+      <c r="K54" s="43" t="inlineStr"/>
+      <c r="L54" s="44" t="inlineStr"/>
+      <c r="M54" s="45" t="inlineStr"/>
       <c r="N54" s="44" t="inlineStr"/>
-      <c r="O54" s="45" t="inlineStr">
-        <is>
-          <t>Evap thermistor sig</t>
-        </is>
-      </c>
+      <c r="O54" s="45" t="inlineStr"/>
       <c r="P54" s="45" t="inlineStr"/>
       <c r="Q54" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B32</t>
+          <t>DRB102.3</t>
         </is>
       </c>
       <c r="R54" s="47" t="inlineStr">
         <is>
-          <t>Evap temp signal (ECU-B B32)</t>
-        </is>
-      </c>
-      <c r="S54" s="48" t="inlineStr">
-        <is>
-          <t>sp_evap</t>
-        </is>
-      </c>
+          <t>spare (DRB102 3)</t>
+        </is>
+      </c>
+      <c r="S54" s="48" t="inlineStr"/>
       <c r="T54" s="48" t="inlineStr"/>
-      <c r="U54" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="V54" s="50" t="inlineStr">
-        <is>
-          <t>Gray</t>
-        </is>
-      </c>
+      <c r="U54" s="49" t="inlineStr"/>
+      <c r="V54" s="50" t="inlineStr"/>
       <c r="W54" s="50" t="inlineStr"/>
-      <c r="X54" s="50" t="inlineStr">
-        <is>
-          <t>Blue-Blue-White</t>
-        </is>
-      </c>
+      <c r="X54" s="50" t="inlineStr"/>
       <c r="Y54" s="50" t="inlineStr"/>
       <c r="Z54" s="51" t="inlineStr"/>
       <c r="AA54" s="52" t="inlineStr"/>
@@ -7141,7 +7093,7 @@
       <c r="AD54" s="54" t="inlineStr"/>
       <c r="AE54" s="54" t="inlineStr">
         <is>
-          <t>end t_evap_temp: end row of the wire list (SoT); splice sp_evap: node of the wire list (SoT)</t>
+          <t>DRB102 3 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF54" s="54" t="inlineStr">
@@ -7176,7 +7128,7 @@
         </is>
       </c>
       <c r="H55" s="25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I55" s="26" t="inlineStr">
         <is>
@@ -7192,12 +7144,12 @@
       <c r="P55" s="29" t="inlineStr"/>
       <c r="Q55" s="30" t="inlineStr">
         <is>
-          <t>DRB102.3</t>
+          <t>DRB102.4</t>
         </is>
       </c>
       <c r="R55" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 3)</t>
+          <t>spare (DRB102 4)</t>
         </is>
       </c>
       <c r="S55" s="32" t="inlineStr"/>
@@ -7214,7 +7166,7 @@
       <c r="AD55" s="38" t="inlineStr"/>
       <c r="AE55" s="38" t="inlineStr">
         <is>
-          <t>DRB102 3 = 'spare (size 12)'</t>
+          <t>DRB102 4 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF55" s="38" t="inlineStr">
@@ -7249,7 +7201,7 @@
         </is>
       </c>
       <c r="H56" s="41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I56" s="42" t="inlineStr">
         <is>
@@ -7265,12 +7217,12 @@
       <c r="P56" s="45" t="inlineStr"/>
       <c r="Q56" s="46" t="inlineStr">
         <is>
-          <t>DRB102.4</t>
+          <t>DRB102.5</t>
         </is>
       </c>
       <c r="R56" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 4)</t>
+          <t>spare (DRB102 5)</t>
         </is>
       </c>
       <c r="S56" s="48" t="inlineStr"/>
@@ -7287,7 +7239,7 @@
       <c r="AD56" s="54" t="inlineStr"/>
       <c r="AE56" s="54" t="inlineStr">
         <is>
-          <t>DRB102 4 = 'spare (size 12)'</t>
+          <t>DRB102 5 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF56" s="54" t="inlineStr">
@@ -7322,7 +7274,7 @@
         </is>
       </c>
       <c r="H57" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I57" s="26" t="inlineStr">
         <is>
@@ -7338,12 +7290,12 @@
       <c r="P57" s="29" t="inlineStr"/>
       <c r="Q57" s="30" t="inlineStr">
         <is>
-          <t>DRB102.5</t>
+          <t>DRB102.6</t>
         </is>
       </c>
       <c r="R57" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 5)</t>
+          <t>spare (DRB102 6)</t>
         </is>
       </c>
       <c r="S57" s="32" t="inlineStr"/>
@@ -7360,7 +7312,7 @@
       <c r="AD57" s="38" t="inlineStr"/>
       <c r="AE57" s="38" t="inlineStr">
         <is>
-          <t>DRB102 5 = 'spare (size 12)'</t>
+          <t>DRB102 6 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF57" s="38" t="inlineStr">
@@ -7395,7 +7347,7 @@
         </is>
       </c>
       <c r="H58" s="41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I58" s="42" t="inlineStr">
         <is>
@@ -7411,12 +7363,12 @@
       <c r="P58" s="45" t="inlineStr"/>
       <c r="Q58" s="46" t="inlineStr">
         <is>
-          <t>DRB102.6</t>
+          <t>DRB102.7</t>
         </is>
       </c>
       <c r="R58" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 6)</t>
+          <t>spare (DRB102 7)</t>
         </is>
       </c>
       <c r="S58" s="48" t="inlineStr"/>
@@ -7433,7 +7385,7 @@
       <c r="AD58" s="54" t="inlineStr"/>
       <c r="AE58" s="54" t="inlineStr">
         <is>
-          <t>DRB102 6 = 'spare (size 12)'</t>
+          <t>DRB102 7 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF58" s="54" t="inlineStr">
@@ -7468,7 +7420,7 @@
         </is>
       </c>
       <c r="H59" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I59" s="26" t="inlineStr">
         <is>
@@ -7484,12 +7436,12 @@
       <c r="P59" s="29" t="inlineStr"/>
       <c r="Q59" s="30" t="inlineStr">
         <is>
-          <t>DRB102.7</t>
+          <t>DRB102.8</t>
         </is>
       </c>
       <c r="R59" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 7)</t>
+          <t>spare (DRB102 8)</t>
         </is>
       </c>
       <c r="S59" s="32" t="inlineStr"/>
@@ -7506,7 +7458,7 @@
       <c r="AD59" s="38" t="inlineStr"/>
       <c r="AE59" s="38" t="inlineStr">
         <is>
-          <t>DRB102 7 = 'spare (size 12)'</t>
+          <t>DRB102 8 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF59" s="38" t="inlineStr">
@@ -7541,7 +7493,7 @@
         </is>
       </c>
       <c r="H60" s="41" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="I60" s="42" t="inlineStr">
         <is>
@@ -7557,12 +7509,12 @@
       <c r="P60" s="45" t="inlineStr"/>
       <c r="Q60" s="46" t="inlineStr">
         <is>
-          <t>DRB102.8</t>
+          <t>DRB102.43</t>
         </is>
       </c>
       <c r="R60" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 8)</t>
+          <t>spare (DRB102 43)</t>
         </is>
       </c>
       <c r="S60" s="48" t="inlineStr"/>
@@ -7579,7 +7531,7 @@
       <c r="AD60" s="54" t="inlineStr"/>
       <c r="AE60" s="54" t="inlineStr">
         <is>
-          <t>DRB102 8 = 'spare (size 12)'</t>
+          <t>DRB102 43 = 'spare (size 4)'</t>
         </is>
       </c>
       <c r="AF60" s="54" t="inlineStr">
@@ -7614,7 +7566,7 @@
         </is>
       </c>
       <c r="H61" s="25" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I61" s="26" t="inlineStr">
         <is>
@@ -7630,12 +7582,12 @@
       <c r="P61" s="29" t="inlineStr"/>
       <c r="Q61" s="30" t="inlineStr">
         <is>
-          <t>DRB102.43</t>
+          <t>DRB102.48</t>
         </is>
       </c>
       <c r="R61" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 43)</t>
+          <t>spare (DRB102 48)</t>
         </is>
       </c>
       <c r="S61" s="32" t="inlineStr"/>
@@ -7652,7 +7604,7 @@
       <c r="AD61" s="38" t="inlineStr"/>
       <c r="AE61" s="38" t="inlineStr">
         <is>
-          <t>DRB102 43 = 'spare (size 4)'</t>
+          <t>DRB102 48 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF61" s="38" t="inlineStr">
@@ -7687,7 +7639,7 @@
         </is>
       </c>
       <c r="H62" s="41" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I62" s="42" t="inlineStr">
         <is>
@@ -7703,12 +7655,12 @@
       <c r="P62" s="45" t="inlineStr"/>
       <c r="Q62" s="46" t="inlineStr">
         <is>
-          <t>DRB102.48</t>
+          <t>DRB102.49</t>
         </is>
       </c>
       <c r="R62" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 48)</t>
+          <t>spare (DRB102 49)</t>
         </is>
       </c>
       <c r="S62" s="48" t="inlineStr"/>
@@ -7725,7 +7677,7 @@
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>DRB102 48 = 'spare (size 8)'</t>
+          <t>DRB102 49 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
@@ -7760,7 +7712,7 @@
         </is>
       </c>
       <c r="H63" s="25" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
@@ -7776,12 +7728,12 @@
       <c r="P63" s="29" t="inlineStr"/>
       <c r="Q63" s="30" t="inlineStr">
         <is>
-          <t>DRB102.49</t>
+          <t>DRB102.54</t>
         </is>
       </c>
       <c r="R63" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 49)</t>
+          <t>spare (DRB102 54)</t>
         </is>
       </c>
       <c r="S63" s="32" t="inlineStr"/>
@@ -7798,7 +7750,7 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>DRB102 49 = 'spare (size 8)'</t>
+          <t>DRB102 54 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -7833,7 +7785,7 @@
         </is>
       </c>
       <c r="H64" s="41" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I64" s="42" t="inlineStr">
         <is>
@@ -7849,12 +7801,12 @@
       <c r="P64" s="45" t="inlineStr"/>
       <c r="Q64" s="46" t="inlineStr">
         <is>
-          <t>DRB102.54</t>
+          <t>DRB102.55</t>
         </is>
       </c>
       <c r="R64" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 54)</t>
+          <t>spare (DRB102 55)</t>
         </is>
       </c>
       <c r="S64" s="48" t="inlineStr"/>
@@ -7871,7 +7823,7 @@
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>DRB102 54 = 'spare (size 8)'</t>
+          <t>DRB102 55 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -7906,7 +7858,7 @@
         </is>
       </c>
       <c r="H65" s="25" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
@@ -7922,12 +7874,12 @@
       <c r="P65" s="29" t="inlineStr"/>
       <c r="Q65" s="30" t="inlineStr">
         <is>
-          <t>DRB102.55</t>
+          <t>DRB102.60</t>
         </is>
       </c>
       <c r="R65" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 55)</t>
+          <t>spare (DRB102 60)</t>
         </is>
       </c>
       <c r="S65" s="32" t="inlineStr"/>
@@ -7944,7 +7896,7 @@
       <c r="AD65" s="38" t="inlineStr"/>
       <c r="AE65" s="38" t="inlineStr">
         <is>
-          <t>DRB102 55 = 'spare (size 8)'</t>
+          <t>DRB102 60 = 'spare (size 4)'</t>
         </is>
       </c>
       <c r="AF65" s="38" t="inlineStr">
@@ -7979,7 +7931,7 @@
         </is>
       </c>
       <c r="H66" s="41" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
@@ -7995,12 +7947,12 @@
       <c r="P66" s="45" t="inlineStr"/>
       <c r="Q66" s="46" t="inlineStr">
         <is>
-          <t>DRB102.60</t>
+          <t>DRB102.63</t>
         </is>
       </c>
       <c r="R66" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 60)</t>
+          <t>spare (DRB102 63)</t>
         </is>
       </c>
       <c r="S66" s="48" t="inlineStr"/>
@@ -8017,7 +7969,7 @@
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="54" t="inlineStr">
         <is>
-          <t>DRB102 60 = 'spare (size 4)'</t>
+          <t>DRB102 63 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF66" s="54" t="inlineStr">
@@ -8052,7 +8004,7 @@
         </is>
       </c>
       <c r="H67" s="25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
@@ -8068,12 +8020,12 @@
       <c r="P67" s="29" t="inlineStr"/>
       <c r="Q67" s="30" t="inlineStr">
         <is>
-          <t>DRB102.63</t>
+          <t>DRB102.64</t>
         </is>
       </c>
       <c r="R67" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 63)</t>
+          <t>spare (DRB102 64)</t>
         </is>
       </c>
       <c r="S67" s="32" t="inlineStr"/>
@@ -8090,7 +8042,7 @@
       <c r="AD67" s="38" t="inlineStr"/>
       <c r="AE67" s="38" t="inlineStr">
         <is>
-          <t>DRB102 63 = 'spare (size 16)'</t>
+          <t>DRB102 64 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF67" s="38" t="inlineStr">
@@ -8125,7 +8077,7 @@
         </is>
       </c>
       <c r="H68" s="41" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I68" s="42" t="inlineStr">
         <is>
@@ -8141,12 +8093,12 @@
       <c r="P68" s="45" t="inlineStr"/>
       <c r="Q68" s="46" t="inlineStr">
         <is>
-          <t>DRB102.64</t>
+          <t>DRB102.65</t>
         </is>
       </c>
       <c r="R68" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 64)</t>
+          <t>spare (DRB102 65)</t>
         </is>
       </c>
       <c r="S68" s="48" t="inlineStr"/>
@@ -8163,7 +8115,7 @@
       <c r="AD68" s="54" t="inlineStr"/>
       <c r="AE68" s="54" t="inlineStr">
         <is>
-          <t>DRB102 64 = 'spare (size 16)'</t>
+          <t>DRB102 65 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF68" s="54" t="inlineStr">
@@ -8198,7 +8150,7 @@
         </is>
       </c>
       <c r="H69" s="25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
@@ -8214,12 +8166,12 @@
       <c r="P69" s="29" t="inlineStr"/>
       <c r="Q69" s="30" t="inlineStr">
         <is>
-          <t>DRB102.65</t>
+          <t>DRB102.66</t>
         </is>
       </c>
       <c r="R69" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 65)</t>
+          <t>spare (DRB102 66)</t>
         </is>
       </c>
       <c r="S69" s="32" t="inlineStr"/>
@@ -8236,7 +8188,7 @@
       <c r="AD69" s="38" t="inlineStr"/>
       <c r="AE69" s="38" t="inlineStr">
         <is>
-          <t>DRB102 65 = 'spare (size 16)'</t>
+          <t>DRB102 66 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF69" s="38" t="inlineStr">
@@ -8271,7 +8223,7 @@
         </is>
       </c>
       <c r="H70" s="41" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I70" s="42" t="inlineStr">
         <is>
@@ -8287,12 +8239,12 @@
       <c r="P70" s="45" t="inlineStr"/>
       <c r="Q70" s="46" t="inlineStr">
         <is>
-          <t>DRB102.66</t>
+          <t>DRB102.67</t>
         </is>
       </c>
       <c r="R70" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 66)</t>
+          <t>spare (DRB102 67)</t>
         </is>
       </c>
       <c r="S70" s="48" t="inlineStr"/>
@@ -8309,7 +8261,7 @@
       <c r="AD70" s="54" t="inlineStr"/>
       <c r="AE70" s="54" t="inlineStr">
         <is>
-          <t>DRB102 66 = 'spare (size 16)'</t>
+          <t>DRB102 67 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF70" s="54" t="inlineStr">
@@ -8344,7 +8296,7 @@
         </is>
       </c>
       <c r="H71" s="25" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
@@ -8360,12 +8312,12 @@
       <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>DRB102.67</t>
+          <t>DRB102.68</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 67)</t>
+          <t>spare (DRB102 68)</t>
         </is>
       </c>
       <c r="S71" s="32" t="inlineStr"/>
@@ -8382,7 +8334,7 @@
       <c r="AD71" s="38" t="inlineStr"/>
       <c r="AE71" s="38" t="inlineStr">
         <is>
-          <t>DRB102 67 = 'spare (size 16)'</t>
+          <t>DRB102 68 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF71" s="38" t="inlineStr">
@@ -8417,7 +8369,7 @@
         </is>
       </c>
       <c r="H72" s="41" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I72" s="42" t="inlineStr">
         <is>
@@ -8433,12 +8385,12 @@
       <c r="P72" s="45" t="inlineStr"/>
       <c r="Q72" s="46" t="inlineStr">
         <is>
-          <t>DRB102.68</t>
+          <t>DRB102.69</t>
         </is>
       </c>
       <c r="R72" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 68)</t>
+          <t>spare (DRB102 69)</t>
         </is>
       </c>
       <c r="S72" s="48" t="inlineStr"/>
@@ -8455,7 +8407,7 @@
       <c r="AD72" s="54" t="inlineStr"/>
       <c r="AE72" s="54" t="inlineStr">
         <is>
-          <t>DRB102 68 = 'spare (size 16)'</t>
+          <t>DRB102 69 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF72" s="54" t="inlineStr">
@@ -8490,7 +8442,7 @@
         </is>
       </c>
       <c r="H73" s="25" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I73" s="26" t="inlineStr">
         <is>
@@ -8506,12 +8458,12 @@
       <c r="P73" s="29" t="inlineStr"/>
       <c r="Q73" s="30" t="inlineStr">
         <is>
-          <t>DRB102.69</t>
+          <t>DRB102.70</t>
         </is>
       </c>
       <c r="R73" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 69)</t>
+          <t>spare (DRB102 70)</t>
         </is>
       </c>
       <c r="S73" s="32" t="inlineStr"/>
@@ -8528,7 +8480,7 @@
       <c r="AD73" s="38" t="inlineStr"/>
       <c r="AE73" s="38" t="inlineStr">
         <is>
-          <t>DRB102 69 = 'spare (size 16)'</t>
+          <t>DRB102 70 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF73" s="38" t="inlineStr">
@@ -8563,7 +8515,7 @@
         </is>
       </c>
       <c r="H74" s="41" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="I74" s="42" t="inlineStr">
         <is>
@@ -8579,12 +8531,12 @@
       <c r="P74" s="45" t="inlineStr"/>
       <c r="Q74" s="46" t="inlineStr">
         <is>
-          <t>DRB102.70</t>
+          <t>DRB102.79</t>
         </is>
       </c>
       <c r="R74" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 70)</t>
+          <t>spare (DRB102 79)</t>
         </is>
       </c>
       <c r="S74" s="48" t="inlineStr"/>
@@ -8601,7 +8553,7 @@
       <c r="AD74" s="54" t="inlineStr"/>
       <c r="AE74" s="54" t="inlineStr">
         <is>
-          <t>DRB102 70 = 'spare (size 16)'</t>
+          <t>DRB102 79 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF74" s="54" t="inlineStr">
@@ -8636,7 +8588,7 @@
         </is>
       </c>
       <c r="H75" s="25" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I75" s="26" t="inlineStr">
         <is>
@@ -8652,12 +8604,12 @@
       <c r="P75" s="29" t="inlineStr"/>
       <c r="Q75" s="30" t="inlineStr">
         <is>
-          <t>DRB102.79</t>
+          <t>DRB102.80</t>
         </is>
       </c>
       <c r="R75" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 79)</t>
+          <t>spare (DRB102 80)</t>
         </is>
       </c>
       <c r="S75" s="32" t="inlineStr"/>
@@ -8674,7 +8626,7 @@
       <c r="AD75" s="38" t="inlineStr"/>
       <c r="AE75" s="38" t="inlineStr">
         <is>
-          <t>DRB102 79 = 'spare (size 16)'</t>
+          <t>DRB102 80 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF75" s="38" t="inlineStr">
@@ -8709,7 +8661,7 @@
         </is>
       </c>
       <c r="H76" s="41" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I76" s="42" t="inlineStr">
         <is>
@@ -8725,12 +8677,12 @@
       <c r="P76" s="45" t="inlineStr"/>
       <c r="Q76" s="46" t="inlineStr">
         <is>
-          <t>DRB102.80</t>
+          <t>DRB102.81</t>
         </is>
       </c>
       <c r="R76" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 80)</t>
+          <t>spare (DRB102 81)</t>
         </is>
       </c>
       <c r="S76" s="48" t="inlineStr"/>
@@ -8747,7 +8699,7 @@
       <c r="AD76" s="54" t="inlineStr"/>
       <c r="AE76" s="54" t="inlineStr">
         <is>
-          <t>DRB102 80 = 'spare (size 16)'</t>
+          <t>DRB102 81 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF76" s="54" t="inlineStr">
@@ -8782,7 +8734,7 @@
         </is>
       </c>
       <c r="H77" s="25" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I77" s="26" t="inlineStr">
         <is>
@@ -8798,12 +8750,12 @@
       <c r="P77" s="29" t="inlineStr"/>
       <c r="Q77" s="30" t="inlineStr">
         <is>
-          <t>DRB102.81</t>
+          <t>DRB102.82</t>
         </is>
       </c>
       <c r="R77" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 81)</t>
+          <t>spare (DRB102 82)</t>
         </is>
       </c>
       <c r="S77" s="32" t="inlineStr"/>
@@ -8820,7 +8772,7 @@
       <c r="AD77" s="38" t="inlineStr"/>
       <c r="AE77" s="38" t="inlineStr">
         <is>
-          <t>DRB102 81 = 'spare (size 16)'</t>
+          <t>DRB102 82 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF77" s="38" t="inlineStr">
@@ -8855,7 +8807,7 @@
         </is>
       </c>
       <c r="H78" s="41" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="I78" s="42" t="inlineStr">
         <is>
@@ -8871,12 +8823,12 @@
       <c r="P78" s="45" t="inlineStr"/>
       <c r="Q78" s="46" t="inlineStr">
         <is>
-          <t>DRB102.82</t>
+          <t>DRB102.97</t>
         </is>
       </c>
       <c r="R78" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 82)</t>
+          <t>spare (DRB102 97)</t>
         </is>
       </c>
       <c r="S78" s="48" t="inlineStr"/>
@@ -8893,7 +8845,7 @@
       <c r="AD78" s="54" t="inlineStr"/>
       <c r="AE78" s="54" t="inlineStr">
         <is>
-          <t>DRB102 82 = 'spare (size 16)'</t>
+          <t>DRB102 97 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF78" s="54" t="inlineStr">
@@ -8928,7 +8880,7 @@
         </is>
       </c>
       <c r="H79" s="25" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I79" s="26" t="inlineStr">
         <is>
@@ -8944,12 +8896,12 @@
       <c r="P79" s="29" t="inlineStr"/>
       <c r="Q79" s="30" t="inlineStr">
         <is>
-          <t>DRB102.97</t>
+          <t>DRB102.98</t>
         </is>
       </c>
       <c r="R79" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 97)</t>
+          <t>spare (DRB102 98)</t>
         </is>
       </c>
       <c r="S79" s="32" t="inlineStr"/>
@@ -8966,7 +8918,7 @@
       <c r="AD79" s="38" t="inlineStr"/>
       <c r="AE79" s="38" t="inlineStr">
         <is>
-          <t>DRB102 97 = 'spare (size 12)'</t>
+          <t>DRB102 98 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF79" s="38" t="inlineStr">
@@ -9001,7 +8953,7 @@
         </is>
       </c>
       <c r="H80" s="41" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I80" s="42" t="inlineStr">
         <is>
@@ -9017,12 +8969,12 @@
       <c r="P80" s="45" t="inlineStr"/>
       <c r="Q80" s="46" t="inlineStr">
         <is>
-          <t>DRB102.98</t>
+          <t>DRB102.99</t>
         </is>
       </c>
       <c r="R80" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 98)</t>
+          <t>spare (DRB102 99)</t>
         </is>
       </c>
       <c r="S80" s="48" t="inlineStr"/>
@@ -9039,7 +8991,7 @@
       <c r="AD80" s="54" t="inlineStr"/>
       <c r="AE80" s="54" t="inlineStr">
         <is>
-          <t>DRB102 98 = 'spare (size 12)'</t>
+          <t>DRB102 99 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF80" s="54" t="inlineStr">
@@ -9074,7 +9026,7 @@
         </is>
       </c>
       <c r="H81" s="25" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I81" s="26" t="inlineStr">
         <is>
@@ -9090,12 +9042,12 @@
       <c r="P81" s="29" t="inlineStr"/>
       <c r="Q81" s="30" t="inlineStr">
         <is>
-          <t>DRB102.99</t>
+          <t>DRB102.100</t>
         </is>
       </c>
       <c r="R81" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 99)</t>
+          <t>spare (DRB102 100)</t>
         </is>
       </c>
       <c r="S81" s="32" t="inlineStr"/>
@@ -9112,7 +9064,7 @@
       <c r="AD81" s="38" t="inlineStr"/>
       <c r="AE81" s="38" t="inlineStr">
         <is>
-          <t>DRB102 99 = 'spare (size 12)'</t>
+          <t>DRB102 100 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF81" s="38" t="inlineStr">
@@ -9147,7 +9099,7 @@
         </is>
       </c>
       <c r="H82" s="41" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I82" s="42" t="inlineStr">
         <is>
@@ -9163,12 +9115,12 @@
       <c r="P82" s="45" t="inlineStr"/>
       <c r="Q82" s="46" t="inlineStr">
         <is>
-          <t>DRB102.100</t>
+          <t>DRB102.101</t>
         </is>
       </c>
       <c r="R82" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 100)</t>
+          <t>spare (DRB102 101)</t>
         </is>
       </c>
       <c r="S82" s="48" t="inlineStr"/>
@@ -9185,7 +9137,7 @@
       <c r="AD82" s="54" t="inlineStr"/>
       <c r="AE82" s="54" t="inlineStr">
         <is>
-          <t>DRB102 100 = 'spare (size 12)'</t>
+          <t>DRB102 101 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF82" s="54" t="inlineStr">
@@ -9220,7 +9172,7 @@
         </is>
       </c>
       <c r="H83" s="25" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I83" s="26" t="inlineStr">
         <is>
@@ -9236,12 +9188,12 @@
       <c r="P83" s="29" t="inlineStr"/>
       <c r="Q83" s="30" t="inlineStr">
         <is>
-          <t>DRB102.101</t>
+          <t>DRB102.102</t>
         </is>
       </c>
       <c r="R83" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 101)</t>
+          <t>spare (DRB102 102)</t>
         </is>
       </c>
       <c r="S83" s="32" t="inlineStr"/>
@@ -9258,7 +9210,7 @@
       <c r="AD83" s="38" t="inlineStr"/>
       <c r="AE83" s="38" t="inlineStr">
         <is>
-          <t>DRB102 101 = 'spare (size 12)'</t>
+          <t>DRB102 102 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF83" s="38" t="inlineStr">
@@ -9284,20 +9236,22 @@
       </c>
       <c r="F84" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G84" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H84" s="41" t="n">
-        <v>102</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H84" s="41" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="I84" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J84" s="42" t="inlineStr"/>
@@ -9309,12 +9263,12 @@
       <c r="P84" s="45" t="inlineStr"/>
       <c r="Q84" s="46" t="inlineStr">
         <is>
-          <t>DRB102.102</t>
+          <t>ECU-B.B1</t>
         </is>
       </c>
       <c r="R84" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 102)</t>
+          <t>spare (ECU-B B1)</t>
         </is>
       </c>
       <c r="S84" s="48" t="inlineStr"/>
@@ -9329,11 +9283,7 @@
       <c r="AB84" s="53" t="inlineStr"/>
       <c r="AC84" s="54" t="inlineStr"/>
       <c r="AD84" s="54" t="inlineStr"/>
-      <c r="AE84" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 102 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE84" s="54" t="inlineStr"/>
       <c r="AF84" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9367,7 +9317,7 @@
       </c>
       <c r="H85" s="25" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="I85" s="26" t="inlineStr">
@@ -9384,12 +9334,12 @@
       <c r="P85" s="29" t="inlineStr"/>
       <c r="Q85" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B1</t>
+          <t>ECU-B.B2</t>
         </is>
       </c>
       <c r="R85" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-B B1)</t>
+          <t>spare (ECU-B B2)</t>
         </is>
       </c>
       <c r="S85" s="32" t="inlineStr"/>
@@ -9438,7 +9388,7 @@
       </c>
       <c r="H86" s="41" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="I86" s="42" t="inlineStr">
@@ -9455,12 +9405,12 @@
       <c r="P86" s="45" t="inlineStr"/>
       <c r="Q86" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B2</t>
+          <t>ECU-B.B3</t>
         </is>
       </c>
       <c r="R86" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-B B2)</t>
+          <t>spare (ECU-B B3)</t>
         </is>
       </c>
       <c r="S86" s="48" t="inlineStr"/>
@@ -9509,7 +9459,7 @@
       </c>
       <c r="H87" s="25" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="I87" s="26" t="inlineStr">
@@ -9526,12 +9476,12 @@
       <c r="P87" s="29" t="inlineStr"/>
       <c r="Q87" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B3</t>
+          <t>ECU-B.B4</t>
         </is>
       </c>
       <c r="R87" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-B B3)</t>
+          <t>spare (ECU-B B4)</t>
         </is>
       </c>
       <c r="S87" s="32" t="inlineStr"/>
@@ -9580,7 +9530,7 @@
       </c>
       <c r="H88" s="41" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B8</t>
         </is>
       </c>
       <c r="I88" s="42" t="inlineStr">
@@ -9597,12 +9547,12 @@
       <c r="P88" s="45" t="inlineStr"/>
       <c r="Q88" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B4</t>
+          <t>ECU-B.B8</t>
         </is>
       </c>
       <c r="R88" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-B B4)</t>
+          <t>spare (ECU-B B8)</t>
         </is>
       </c>
       <c r="S88" s="48" t="inlineStr"/>
@@ -9651,7 +9601,7 @@
       </c>
       <c r="H89" s="25" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="I89" s="26" t="inlineStr">
@@ -9668,12 +9618,12 @@
       <c r="P89" s="29" t="inlineStr"/>
       <c r="Q89" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B8</t>
+          <t>ECU-B.B11</t>
         </is>
       </c>
       <c r="R89" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-B B8)</t>
+          <t>spare (ECU-B B11)</t>
         </is>
       </c>
       <c r="S89" s="32" t="inlineStr"/>
@@ -9722,7 +9672,7 @@
       </c>
       <c r="H90" s="41" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B14</t>
         </is>
       </c>
       <c r="I90" s="42" t="inlineStr">
@@ -9739,12 +9689,12 @@
       <c r="P90" s="45" t="inlineStr"/>
       <c r="Q90" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B11</t>
+          <t>ECU-B.B14</t>
         </is>
       </c>
       <c r="R90" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-B B11)</t>
+          <t>spare (ECU-B B14)</t>
         </is>
       </c>
       <c r="S90" s="48" t="inlineStr"/>
@@ -9783,22 +9733,20 @@
       </c>
       <c r="F91" s="25" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>ix_ws_rear_p</t>
         </is>
       </c>
       <c r="G91" s="26" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H91" s="25" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
+          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
+        </is>
+      </c>
+      <c r="H91" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="I91" s="26" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J91" s="26" t="inlineStr"/>
@@ -9810,12 +9758,12 @@
       <c r="P91" s="29" t="inlineStr"/>
       <c r="Q91" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B14</t>
+          <t>ix_ws_rear_p.6</t>
         </is>
       </c>
       <c r="R91" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-B B14)</t>
+          <t>spare (ix_ws_rear_p 6)</t>
         </is>
       </c>
       <c r="S91" s="32" t="inlineStr"/>
@@ -9838,77 +9786,8 @@
       </c>
       <c r="AG91" s="38" t="inlineStr"/>
     </row>
-    <row r="92">
-      <c r="A92" s="39" t="inlineStr"/>
-      <c r="B92" s="39" t="inlineStr"/>
-      <c r="C92" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D92" s="39" t="inlineStr"/>
-      <c r="E92" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F92" s="41" t="inlineStr">
-        <is>
-          <t>ix_ws_rear_p</t>
-        </is>
-      </c>
-      <c r="G92" s="42" t="inlineStr">
-        <is>
-          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
-        </is>
-      </c>
-      <c r="H92" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="I92" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J92" s="42" t="inlineStr"/>
-      <c r="K92" s="43" t="inlineStr"/>
-      <c r="L92" s="44" t="inlineStr"/>
-      <c r="M92" s="45" t="inlineStr"/>
-      <c r="N92" s="44" t="inlineStr"/>
-      <c r="O92" s="45" t="inlineStr"/>
-      <c r="P92" s="45" t="inlineStr"/>
-      <c r="Q92" s="46" t="inlineStr">
-        <is>
-          <t>ix_ws_rear_p.6</t>
-        </is>
-      </c>
-      <c r="R92" s="47" t="inlineStr">
-        <is>
-          <t>spare (ix_ws_rear_p 6)</t>
-        </is>
-      </c>
-      <c r="S92" s="48" t="inlineStr"/>
-      <c r="T92" s="48" t="inlineStr"/>
-      <c r="U92" s="49" t="inlineStr"/>
-      <c r="V92" s="50" t="inlineStr"/>
-      <c r="W92" s="50" t="inlineStr"/>
-      <c r="X92" s="50" t="inlineStr"/>
-      <c r="Y92" s="50" t="inlineStr"/>
-      <c r="Z92" s="51" t="inlineStr"/>
-      <c r="AA92" s="52" t="inlineStr"/>
-      <c r="AB92" s="53" t="inlineStr"/>
-      <c r="AC92" s="54" t="inlineStr"/>
-      <c r="AD92" s="54" t="inlineStr"/>
-      <c r="AE92" s="54" t="inlineStr"/>
-      <c r="AF92" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG92" s="54" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:AG92"/>
+  <autoFilter ref="A2:AG91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -9929,7 +9808,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
@@ -10144,18 +10023,18 @@
         </is>
       </c>
       <c r="F4" s="48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G4" s="48" t="inlineStr">
         <is>
-          <t>20+20+20+20+20 + shield</t>
+          <t>20+20+20+20 + shield</t>
         </is>
       </c>
       <c r="H4" s="48" t="n">
-        <v>5110</v>
+        <v>4088</v>
       </c>
       <c r="I4" s="48" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4" s="58" t="inlineStr">
         <is>
@@ -11919,7 +11798,7 @@
       </c>
       <c r="I24" s="61" t="inlineStr">
         <is>
-          <t>Screen B (ECU B17, SHIELD_B)</t>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
         </is>
       </c>
       <c r="J24" s="62" t="inlineStr">

--- a/docs/harness/wirelist/B-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/B-cabin-wirelist.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$92</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Connectors'!$A$2:$G$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Connectors'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG91"/>
+  <dimension ref="A1:AG92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -759,14 +759,14 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="36" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="32" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
     <col width="18" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L30" s="44" t="inlineStr">
         <is>
-          <t>sp_shield_b</t>
+          <t>sp_shield_b_wsr</t>
         </is>
       </c>
       <c r="M30" s="45" t="inlineStr">
         <is>
-          <t>splice sp_shield_b (SP-SHIELD-B)</t>
+          <t>splice sp_shield_b_wsr (SP-SHIELD-B-WSR)</t>
         </is>
       </c>
       <c r="N30" s="44" t="inlineStr"/>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="S30" s="48" t="inlineStr">
         <is>
-          <t>sp_shield_b</t>
+          <t>sp_shield_b_wsr</t>
         </is>
       </c>
       <c r="T30" s="48" t="inlineStr">
@@ -4341,7 +4341,7 @@
       <c r="AD30" s="54" t="inlineStr"/>
       <c r="AE30" s="54" t="inlineStr">
         <is>
-          <t>splice sp_shield_b: node of the wire list (SoT)</t>
+          <t>splice sp_shield_b_wsr: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF30" s="54" t="inlineStr">
@@ -6581,12 +6581,12 @@
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>SHLD</t>
         </is>
       </c>
       <c r="B50" s="39" t="inlineStr">
         <is>
-          <t>cab_canbh_bc_sh</t>
+          <t>w_shd_b_wsr</t>
         </is>
       </c>
       <c r="C50" s="39" t="inlineStr">
@@ -6594,11 +6594,7 @@
           <t>B-cabin</t>
         </is>
       </c>
-      <c r="D50" s="39" t="inlineStr">
-        <is>
-          <t>CAN</t>
-        </is>
-      </c>
+      <c r="D50" s="39" t="inlineStr"/>
       <c r="E50" s="40" t="inlineStr">
         <is>
           <t>splice</t>
@@ -6606,80 +6602,78 @@
       </c>
       <c r="F50" s="41" t="inlineStr">
         <is>
-          <t>sp_can_sh_bh</t>
+          <t>sp_shield_b_wsr</t>
         </is>
       </c>
       <c r="G50" s="42" t="inlineStr">
         <is>
-          <t>splice sp_can_sh_bh (SP-CAN-SH-BH)</t>
+          <t>splice sp_shield_b_wsr (SP-SHIELD-B-WSR)</t>
         </is>
       </c>
       <c r="H50" s="41" t="inlineStr"/>
       <c r="I50" s="42" t="inlineStr">
         <is>
-          <t>CAN-Lambda shield</t>
+          <t>Shield drain B</t>
         </is>
       </c>
       <c r="J50" s="42" t="inlineStr"/>
       <c r="K50" s="43" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="L50" s="44" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>sp_shield_b</t>
         </is>
       </c>
       <c r="M50" s="45" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="N50" s="44" t="n">
-        <v>94</v>
-      </c>
+          <t>splice sp_shield_b (SP-SHIELD-B)</t>
+        </is>
+      </c>
+      <c r="N50" s="44" t="inlineStr"/>
       <c r="O50" s="45" t="inlineStr">
         <is>
-          <t>CAN-Lambda shield</t>
+          <t>Shield drain B</t>
         </is>
       </c>
       <c r="P50" s="45" t="inlineStr"/>
       <c r="Q50" s="46" t="inlineStr">
         <is>
-          <t>ECU-COMMS.C1</t>
+          <t>ECU-B.B17</t>
         </is>
       </c>
       <c r="R50" s="47" t="inlineStr">
         <is>
-          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+          <t>Screen B (ECU B17, SHIELD_B)</t>
         </is>
       </c>
       <c r="S50" s="48" t="inlineStr">
         <is>
-          <t>sp_can_sh_bh</t>
-        </is>
-      </c>
-      <c r="T50" s="48" t="inlineStr">
-        <is>
-          <t>cab_canbh_bc</t>
-        </is>
-      </c>
-      <c r="U50" s="49" t="inlineStr"/>
+          <t>sp_shield_b</t>
+        </is>
+      </c>
+      <c r="T50" s="48" t="inlineStr"/>
+      <c r="U50" s="49" t="n">
+        <v>20</v>
+      </c>
       <c r="V50" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W50" s="50" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W50" s="50" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
       <c r="X50" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="Y50" s="50" t="n">
-        <v>120</v>
-      </c>
+          <t>White-Yellow-Blue</t>
+        </is>
+      </c>
+      <c r="Y50" s="50" t="inlineStr"/>
       <c r="Z50" s="51" t="inlineStr"/>
       <c r="AA50" s="52" t="inlineStr"/>
       <c r="AB50" s="53" t="inlineStr"/>
@@ -6687,7 +6681,7 @@
       <c r="AD50" s="54" t="inlineStr"/>
       <c r="AE50" s="54" t="inlineStr">
         <is>
-          <t>splice sp_can_sh_bh: node of the wire list (SoT); DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to ECU C1, via the CAN'</t>
+          <t>splice sp_shield_b_wsr: node of the wire list (SoT); splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF50" s="54" t="inlineStr">
@@ -6697,19 +6691,19 @@
       </c>
       <c r="AG50" s="54" t="inlineStr">
         <is>
-          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on B-cabin, 120 mm)</t>
+          <t>branch-point join (R207): the device drain meets the loom shield trunk where its signal wires join the main loom, then runs to the ECU splice</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>ACBTN</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>w_ac_btn_in</t>
+          <t>cab_canbh_bc_sh</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
@@ -6717,80 +6711,92 @@
           <t>B-cabin</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr"/>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>CAN</t>
+        </is>
+      </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>terminal</t>
+          <t>splice</t>
         </is>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>t_ac_btn</t>
+          <t>sp_can_sh_bh</t>
         </is>
       </c>
       <c r="G51" s="26" t="inlineStr">
         <is>
-          <t>OEM dash A/C switch V-G lead (old A15 pin 3)</t>
+          <t>splice sp_can_sh_bh (SP-CAN-SH-BH)</t>
         </is>
       </c>
       <c r="H51" s="25" t="inlineStr"/>
       <c r="I51" s="26" t="inlineStr">
         <is>
-          <t>A/C switch V-G in</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="J51" s="26" t="inlineStr"/>
       <c r="K51" s="27" t="inlineStr">
         <is>
-          <t>resistor</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="L51" s="28" t="inlineStr">
         <is>
-          <t>r_ac_btn_hi</t>
+          <t>bh_b_fw</t>
         </is>
       </c>
       <c r="M51" s="29" t="inlineStr">
         <is>
-          <t>10k A/C switch divider, top</t>
+          <t>BH-B (firewall bulkhead DRB102, RH)</t>
         </is>
       </c>
       <c r="N51" s="28" t="n">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
-          <t>A/C switch V-G in</t>
+          <t>CAN-Lambda shield</t>
         </is>
       </c>
       <c r="P51" s="29" t="inlineStr"/>
       <c r="Q51" s="30" t="inlineStr">
         <is>
-          <t>r_ac_btn_hi.1</t>
+          <t>ECU-COMMS.C1</t>
         </is>
       </c>
       <c r="R51" s="31" t="inlineStr">
         <is>
-          <t>A/C switch V-G in (r_ac_btn_hi 1)</t>
-        </is>
-      </c>
-      <c r="S51" s="32" t="inlineStr"/>
-      <c r="T51" s="32" t="inlineStr"/>
-      <c r="U51" s="33" t="n">
-        <v>20</v>
-      </c>
+          <t>Screen CAN (ECU C1, CAN_SCREEN)</t>
+        </is>
+      </c>
+      <c r="S51" s="32" t="inlineStr">
+        <is>
+          <t>sp_can_sh_bh</t>
+        </is>
+      </c>
+      <c r="T51" s="32" t="inlineStr">
+        <is>
+          <t>cab_canbh_bc</t>
+        </is>
+      </c>
+      <c r="U51" s="33" t="inlineStr"/>
       <c r="V51" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Shield</t>
         </is>
       </c>
       <c r="W51" s="34" t="inlineStr"/>
       <c r="X51" s="34" t="inlineStr">
         <is>
-          <t>Blue-Blue-Yellow</t>
-        </is>
-      </c>
-      <c r="Y51" s="34" t="inlineStr"/>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="Y51" s="34" t="n">
+        <v>120</v>
+      </c>
       <c r="Z51" s="35" t="inlineStr"/>
       <c r="AA51" s="36" t="inlineStr"/>
       <c r="AB51" s="37" t="inlineStr"/>
@@ -6798,7 +6804,7 @@
       <c r="AD51" s="38" t="inlineStr"/>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>end t_ac_btn: end row of the wire list (SoT)</t>
+          <t>splice sp_can_sh_bh: node of the wire list (SoT); DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to ECU C1, via the CAN'</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -6806,17 +6812,21 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AG51" s="38" t="inlineStr"/>
+      <c r="AG51" s="38" t="inlineStr">
+        <is>
+          <t>owner TBD: a half has no length estimate (drawn today as cab_can_bh_sh on CAN, ? mm; cab_canbh_bc_sh on B-cabin, 120 mm)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>SGND</t>
+          <t>ACBTN</t>
         </is>
       </c>
       <c r="B52" s="39" t="inlineStr">
         <is>
-          <t>w_evap_rtn</t>
+          <t>w_ac_btn_in</t>
         </is>
       </c>
       <c r="C52" s="39" t="inlineStr">
@@ -6832,75 +6842,69 @@
       </c>
       <c r="F52" s="41" t="inlineStr">
         <is>
-          <t>t_evap_rtn</t>
+          <t>t_ac_btn</t>
         </is>
       </c>
       <c r="G52" s="42" t="inlineStr">
         <is>
-          <t>OEM evaporator thermistor A24 pin 2, at the evap case</t>
+          <t>OEM dash A/C switch V-G lead (old A15 pin 3)</t>
         </is>
       </c>
       <c r="H52" s="41" t="inlineStr"/>
       <c r="I52" s="42" t="inlineStr">
         <is>
-          <t>Evap thermistor gnd</t>
+          <t>A/C switch V-G in</t>
         </is>
       </c>
       <c r="J52" s="42" t="inlineStr"/>
       <c r="K52" s="43" t="inlineStr">
         <is>
-          <t>splice</t>
+          <t>resistor</t>
         </is>
       </c>
       <c r="L52" s="44" t="inlineStr">
         <is>
-          <t>sp_gndout_b</t>
+          <t>r_ac_btn_hi</t>
         </is>
       </c>
       <c r="M52" s="45" t="inlineStr">
         <is>
-          <t>splice sp_gndout_b (SP-GNDOUT-B)</t>
-        </is>
-      </c>
-      <c r="N52" s="44" t="inlineStr"/>
+          <t>10k A/C switch divider, top</t>
+        </is>
+      </c>
+      <c r="N52" s="44" t="n">
+        <v>1</v>
+      </c>
       <c r="O52" s="45" t="inlineStr">
         <is>
-          <t>Evap thermistor gnd</t>
+          <t>A/C switch V-G in</t>
         </is>
       </c>
       <c r="P52" s="45" t="inlineStr"/>
       <c r="Q52" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B22</t>
+          <t>r_ac_btn_hi.1</t>
         </is>
       </c>
       <c r="R52" s="47" t="inlineStr">
         <is>
-          <t>Sensor GND B (ECU-B B22)</t>
-        </is>
-      </c>
-      <c r="S52" s="48" t="inlineStr">
-        <is>
-          <t>sp_gndout_b</t>
-        </is>
-      </c>
+          <t>A/C switch V-G in (r_ac_btn_hi 1)</t>
+        </is>
+      </c>
+      <c r="S52" s="48" t="inlineStr"/>
       <c r="T52" s="48" t="inlineStr"/>
       <c r="U52" s="49" t="n">
         <v>20</v>
       </c>
       <c r="V52" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W52" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Gray</t>
+        </is>
+      </c>
+      <c r="W52" s="50" t="inlineStr"/>
       <c r="X52" s="50" t="inlineStr">
         <is>
-          <t>Yellow-Yellow-Blue</t>
+          <t>Blue-Blue-Yellow</t>
         </is>
       </c>
       <c r="Y52" s="50" t="inlineStr"/>
@@ -6911,7 +6915,7 @@
       <c r="AD52" s="54" t="inlineStr"/>
       <c r="AE52" s="54" t="inlineStr">
         <is>
-          <t>end t_evap_rtn: end row of the wire list (SoT); splice sp_gndout_b: node of the wire list (SoT)</t>
+          <t>end t_ac_btn: end row of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF52" s="54" t="inlineStr">
@@ -6924,12 +6928,12 @@
     <row r="53">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>EVAP</t>
+          <t>SGND</t>
         </is>
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>w_evap_sig</t>
+          <t>w_evap_rtn</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
@@ -6945,18 +6949,18 @@
       </c>
       <c r="F53" s="25" t="inlineStr">
         <is>
-          <t>t_evap_temp</t>
+          <t>t_evap_rtn</t>
         </is>
       </c>
       <c r="G53" s="26" t="inlineStr">
         <is>
-          <t>OEM evaporator thermistor A24 pin 1, at the evap case</t>
+          <t>OEM evaporator thermistor A24 pin 2, at the evap case</t>
         </is>
       </c>
       <c r="H53" s="25" t="inlineStr"/>
       <c r="I53" s="26" t="inlineStr">
         <is>
-          <t>Evap thermistor sig</t>
+          <t>Evap thermistor gnd</t>
         </is>
       </c>
       <c r="J53" s="26" t="inlineStr"/>
@@ -6967,34 +6971,34 @@
       </c>
       <c r="L53" s="28" t="inlineStr">
         <is>
-          <t>sp_evap</t>
+          <t>sp_gndout_b</t>
         </is>
       </c>
       <c r="M53" s="29" t="inlineStr">
         <is>
-          <t>splice sp_evap (SP-EVAP)</t>
+          <t>splice sp_gndout_b (SP-GNDOUT-B)</t>
         </is>
       </c>
       <c r="N53" s="28" t="inlineStr"/>
       <c r="O53" s="29" t="inlineStr">
         <is>
-          <t>Evap thermistor sig</t>
+          <t>Evap thermistor gnd</t>
         </is>
       </c>
       <c r="P53" s="29" t="inlineStr"/>
       <c r="Q53" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B32</t>
+          <t>ECU-B.B22</t>
         </is>
       </c>
       <c r="R53" s="31" t="inlineStr">
         <is>
-          <t>Evap temp signal (ECU-B B32)</t>
+          <t>Sensor GND B (ECU-B B22)</t>
         </is>
       </c>
       <c r="S53" s="32" t="inlineStr">
         <is>
-          <t>sp_evap</t>
+          <t>sp_gndout_b</t>
         </is>
       </c>
       <c r="T53" s="32" t="inlineStr"/>
@@ -7003,13 +7007,17 @@
       </c>
       <c r="V53" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
-        </is>
-      </c>
-      <c r="W53" s="34" t="inlineStr"/>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W53" s="34" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
       <c r="X53" s="34" t="inlineStr">
         <is>
-          <t>Blue-Blue-White</t>
+          <t>Yellow-Yellow-Blue</t>
         </is>
       </c>
       <c r="Y53" s="34" t="inlineStr"/>
@@ -7020,7 +7028,7 @@
       <c r="AD53" s="38" t="inlineStr"/>
       <c r="AE53" s="38" t="inlineStr">
         <is>
-          <t>end t_evap_temp: end row of the wire list (SoT); splice sp_evap: node of the wire list (SoT)</t>
+          <t>end t_evap_rtn: end row of the wire list (SoT); splice sp_gndout_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF53" s="38" t="inlineStr">
@@ -7031,8 +7039,16 @@
       <c r="AG53" s="38" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="39" t="inlineStr"/>
-      <c r="B54" s="39" t="inlineStr"/>
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>EVAP</t>
+        </is>
+      </c>
+      <c r="B54" s="39" t="inlineStr">
+        <is>
+          <t>w_evap_sig</t>
+        </is>
+      </c>
       <c r="C54" s="39" t="inlineStr">
         <is>
           <t>B-cabin</t>
@@ -7041,50 +7057,78 @@
       <c r="D54" s="39" t="inlineStr"/>
       <c r="E54" s="40" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>terminal</t>
         </is>
       </c>
       <c r="F54" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>t_evap_temp</t>
         </is>
       </c>
       <c r="G54" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H54" s="41" t="n">
-        <v>3</v>
-      </c>
+          <t>OEM evaporator thermistor A24 pin 1, at the evap case</t>
+        </is>
+      </c>
+      <c r="H54" s="41" t="inlineStr"/>
       <c r="I54" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>Evap thermistor sig</t>
         </is>
       </c>
       <c r="J54" s="42" t="inlineStr"/>
-      <c r="K54" s="43" t="inlineStr"/>
-      <c r="L54" s="44" t="inlineStr"/>
-      <c r="M54" s="45" t="inlineStr"/>
+      <c r="K54" s="43" t="inlineStr">
+        <is>
+          <t>splice</t>
+        </is>
+      </c>
+      <c r="L54" s="44" t="inlineStr">
+        <is>
+          <t>sp_evap</t>
+        </is>
+      </c>
+      <c r="M54" s="45" t="inlineStr">
+        <is>
+          <t>splice sp_evap (SP-EVAP)</t>
+        </is>
+      </c>
       <c r="N54" s="44" t="inlineStr"/>
-      <c r="O54" s="45" t="inlineStr"/>
+      <c r="O54" s="45" t="inlineStr">
+        <is>
+          <t>Evap thermistor sig</t>
+        </is>
+      </c>
       <c r="P54" s="45" t="inlineStr"/>
       <c r="Q54" s="46" t="inlineStr">
         <is>
-          <t>DRB102.3</t>
+          <t>ECU-B.B32</t>
         </is>
       </c>
       <c r="R54" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 3)</t>
-        </is>
-      </c>
-      <c r="S54" s="48" t="inlineStr"/>
+          <t>Evap temp signal (ECU-B B32)</t>
+        </is>
+      </c>
+      <c r="S54" s="48" t="inlineStr">
+        <is>
+          <t>sp_evap</t>
+        </is>
+      </c>
       <c r="T54" s="48" t="inlineStr"/>
-      <c r="U54" s="49" t="inlineStr"/>
-      <c r="V54" s="50" t="inlineStr"/>
+      <c r="U54" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="V54" s="50" t="inlineStr">
+        <is>
+          <t>Gray</t>
+        </is>
+      </c>
       <c r="W54" s="50" t="inlineStr"/>
-      <c r="X54" s="50" t="inlineStr"/>
+      <c r="X54" s="50" t="inlineStr">
+        <is>
+          <t>Blue-Blue-White</t>
+        </is>
+      </c>
       <c r="Y54" s="50" t="inlineStr"/>
       <c r="Z54" s="51" t="inlineStr"/>
       <c r="AA54" s="52" t="inlineStr"/>
@@ -7093,7 +7137,7 @@
       <c r="AD54" s="54" t="inlineStr"/>
       <c r="AE54" s="54" t="inlineStr">
         <is>
-          <t>DRB102 3 = 'spare (size 12)'</t>
+          <t>end t_evap_temp: end row of the wire list (SoT); splice sp_evap: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF54" s="54" t="inlineStr">
@@ -7128,7 +7172,7 @@
         </is>
       </c>
       <c r="H55" s="25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I55" s="26" t="inlineStr">
         <is>
@@ -7144,12 +7188,12 @@
       <c r="P55" s="29" t="inlineStr"/>
       <c r="Q55" s="30" t="inlineStr">
         <is>
-          <t>DRB102.4</t>
+          <t>DRB102.3</t>
         </is>
       </c>
       <c r="R55" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 4)</t>
+          <t>spare (DRB102 3)</t>
         </is>
       </c>
       <c r="S55" s="32" t="inlineStr"/>
@@ -7166,7 +7210,7 @@
       <c r="AD55" s="38" t="inlineStr"/>
       <c r="AE55" s="38" t="inlineStr">
         <is>
-          <t>DRB102 4 = 'spare (size 12)'</t>
+          <t>DRB102 3 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF55" s="38" t="inlineStr">
@@ -7201,7 +7245,7 @@
         </is>
       </c>
       <c r="H56" s="41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I56" s="42" t="inlineStr">
         <is>
@@ -7217,12 +7261,12 @@
       <c r="P56" s="45" t="inlineStr"/>
       <c r="Q56" s="46" t="inlineStr">
         <is>
-          <t>DRB102.5</t>
+          <t>DRB102.4</t>
         </is>
       </c>
       <c r="R56" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 5)</t>
+          <t>spare (DRB102 4)</t>
         </is>
       </c>
       <c r="S56" s="48" t="inlineStr"/>
@@ -7239,7 +7283,7 @@
       <c r="AD56" s="54" t="inlineStr"/>
       <c r="AE56" s="54" t="inlineStr">
         <is>
-          <t>DRB102 5 = 'spare (size 12)'</t>
+          <t>DRB102 4 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF56" s="54" t="inlineStr">
@@ -7274,7 +7318,7 @@
         </is>
       </c>
       <c r="H57" s="25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I57" s="26" t="inlineStr">
         <is>
@@ -7290,12 +7334,12 @@
       <c r="P57" s="29" t="inlineStr"/>
       <c r="Q57" s="30" t="inlineStr">
         <is>
-          <t>DRB102.6</t>
+          <t>DRB102.5</t>
         </is>
       </c>
       <c r="R57" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 6)</t>
+          <t>spare (DRB102 5)</t>
         </is>
       </c>
       <c r="S57" s="32" t="inlineStr"/>
@@ -7312,7 +7356,7 @@
       <c r="AD57" s="38" t="inlineStr"/>
       <c r="AE57" s="38" t="inlineStr">
         <is>
-          <t>DRB102 6 = 'spare (size 12)'</t>
+          <t>DRB102 5 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF57" s="38" t="inlineStr">
@@ -7347,7 +7391,7 @@
         </is>
       </c>
       <c r="H58" s="41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I58" s="42" t="inlineStr">
         <is>
@@ -7363,12 +7407,12 @@
       <c r="P58" s="45" t="inlineStr"/>
       <c r="Q58" s="46" t="inlineStr">
         <is>
-          <t>DRB102.7</t>
+          <t>DRB102.6</t>
         </is>
       </c>
       <c r="R58" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 7)</t>
+          <t>spare (DRB102 6)</t>
         </is>
       </c>
       <c r="S58" s="48" t="inlineStr"/>
@@ -7385,7 +7429,7 @@
       <c r="AD58" s="54" t="inlineStr"/>
       <c r="AE58" s="54" t="inlineStr">
         <is>
-          <t>DRB102 7 = 'spare (size 12)'</t>
+          <t>DRB102 6 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF58" s="54" t="inlineStr">
@@ -7420,7 +7464,7 @@
         </is>
       </c>
       <c r="H59" s="25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I59" s="26" t="inlineStr">
         <is>
@@ -7436,12 +7480,12 @@
       <c r="P59" s="29" t="inlineStr"/>
       <c r="Q59" s="30" t="inlineStr">
         <is>
-          <t>DRB102.8</t>
+          <t>DRB102.7</t>
         </is>
       </c>
       <c r="R59" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 8)</t>
+          <t>spare (DRB102 7)</t>
         </is>
       </c>
       <c r="S59" s="32" t="inlineStr"/>
@@ -7458,7 +7502,7 @@
       <c r="AD59" s="38" t="inlineStr"/>
       <c r="AE59" s="38" t="inlineStr">
         <is>
-          <t>DRB102 8 = 'spare (size 12)'</t>
+          <t>DRB102 7 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF59" s="38" t="inlineStr">
@@ -7493,7 +7537,7 @@
         </is>
       </c>
       <c r="H60" s="41" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="I60" s="42" t="inlineStr">
         <is>
@@ -7509,12 +7553,12 @@
       <c r="P60" s="45" t="inlineStr"/>
       <c r="Q60" s="46" t="inlineStr">
         <is>
-          <t>DRB102.43</t>
+          <t>DRB102.8</t>
         </is>
       </c>
       <c r="R60" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 43)</t>
+          <t>spare (DRB102 8)</t>
         </is>
       </c>
       <c r="S60" s="48" t="inlineStr"/>
@@ -7531,7 +7575,7 @@
       <c r="AD60" s="54" t="inlineStr"/>
       <c r="AE60" s="54" t="inlineStr">
         <is>
-          <t>DRB102 43 = 'spare (size 4)'</t>
+          <t>DRB102 8 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF60" s="54" t="inlineStr">
@@ -7566,7 +7610,7 @@
         </is>
       </c>
       <c r="H61" s="25" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I61" s="26" t="inlineStr">
         <is>
@@ -7582,12 +7626,12 @@
       <c r="P61" s="29" t="inlineStr"/>
       <c r="Q61" s="30" t="inlineStr">
         <is>
-          <t>DRB102.48</t>
+          <t>DRB102.43</t>
         </is>
       </c>
       <c r="R61" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 48)</t>
+          <t>spare (DRB102 43)</t>
         </is>
       </c>
       <c r="S61" s="32" t="inlineStr"/>
@@ -7604,7 +7648,7 @@
       <c r="AD61" s="38" t="inlineStr"/>
       <c r="AE61" s="38" t="inlineStr">
         <is>
-          <t>DRB102 48 = 'spare (size 8)'</t>
+          <t>DRB102 43 = 'spare (size 4)'</t>
         </is>
       </c>
       <c r="AF61" s="38" t="inlineStr">
@@ -7639,7 +7683,7 @@
         </is>
       </c>
       <c r="H62" s="41" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I62" s="42" t="inlineStr">
         <is>
@@ -7655,12 +7699,12 @@
       <c r="P62" s="45" t="inlineStr"/>
       <c r="Q62" s="46" t="inlineStr">
         <is>
-          <t>DRB102.49</t>
+          <t>DRB102.48</t>
         </is>
       </c>
       <c r="R62" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 49)</t>
+          <t>spare (DRB102 48)</t>
         </is>
       </c>
       <c r="S62" s="48" t="inlineStr"/>
@@ -7677,7 +7721,7 @@
       <c r="AD62" s="54" t="inlineStr"/>
       <c r="AE62" s="54" t="inlineStr">
         <is>
-          <t>DRB102 49 = 'spare (size 8)'</t>
+          <t>DRB102 48 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF62" s="54" t="inlineStr">
@@ -7712,7 +7756,7 @@
         </is>
       </c>
       <c r="H63" s="25" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
@@ -7728,12 +7772,12 @@
       <c r="P63" s="29" t="inlineStr"/>
       <c r="Q63" s="30" t="inlineStr">
         <is>
-          <t>DRB102.54</t>
+          <t>DRB102.49</t>
         </is>
       </c>
       <c r="R63" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 54)</t>
+          <t>spare (DRB102 49)</t>
         </is>
       </c>
       <c r="S63" s="32" t="inlineStr"/>
@@ -7750,7 +7794,7 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>DRB102 54 = 'spare (size 8)'</t>
+          <t>DRB102 49 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -7785,7 +7829,7 @@
         </is>
       </c>
       <c r="H64" s="41" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I64" s="42" t="inlineStr">
         <is>
@@ -7801,12 +7845,12 @@
       <c r="P64" s="45" t="inlineStr"/>
       <c r="Q64" s="46" t="inlineStr">
         <is>
-          <t>DRB102.55</t>
+          <t>DRB102.54</t>
         </is>
       </c>
       <c r="R64" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 55)</t>
+          <t>spare (DRB102 54)</t>
         </is>
       </c>
       <c r="S64" s="48" t="inlineStr"/>
@@ -7823,7 +7867,7 @@
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>DRB102 55 = 'spare (size 8)'</t>
+          <t>DRB102 54 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -7858,7 +7902,7 @@
         </is>
       </c>
       <c r="H65" s="25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
@@ -7874,12 +7918,12 @@
       <c r="P65" s="29" t="inlineStr"/>
       <c r="Q65" s="30" t="inlineStr">
         <is>
-          <t>DRB102.60</t>
+          <t>DRB102.55</t>
         </is>
       </c>
       <c r="R65" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 60)</t>
+          <t>spare (DRB102 55)</t>
         </is>
       </c>
       <c r="S65" s="32" t="inlineStr"/>
@@ -7896,7 +7940,7 @@
       <c r="AD65" s="38" t="inlineStr"/>
       <c r="AE65" s="38" t="inlineStr">
         <is>
-          <t>DRB102 60 = 'spare (size 4)'</t>
+          <t>DRB102 55 = 'spare (size 8)'</t>
         </is>
       </c>
       <c r="AF65" s="38" t="inlineStr">
@@ -7931,7 +7975,7 @@
         </is>
       </c>
       <c r="H66" s="41" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
@@ -7947,12 +7991,12 @@
       <c r="P66" s="45" t="inlineStr"/>
       <c r="Q66" s="46" t="inlineStr">
         <is>
-          <t>DRB102.63</t>
+          <t>DRB102.60</t>
         </is>
       </c>
       <c r="R66" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 63)</t>
+          <t>spare (DRB102 60)</t>
         </is>
       </c>
       <c r="S66" s="48" t="inlineStr"/>
@@ -7969,7 +8013,7 @@
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="54" t="inlineStr">
         <is>
-          <t>DRB102 63 = 'spare (size 16)'</t>
+          <t>DRB102 60 = 'spare (size 4)'</t>
         </is>
       </c>
       <c r="AF66" s="54" t="inlineStr">
@@ -8004,7 +8048,7 @@
         </is>
       </c>
       <c r="H67" s="25" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
@@ -8020,12 +8064,12 @@
       <c r="P67" s="29" t="inlineStr"/>
       <c r="Q67" s="30" t="inlineStr">
         <is>
-          <t>DRB102.64</t>
+          <t>DRB102.63</t>
         </is>
       </c>
       <c r="R67" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 64)</t>
+          <t>spare (DRB102 63)</t>
         </is>
       </c>
       <c r="S67" s="32" t="inlineStr"/>
@@ -8042,7 +8086,7 @@
       <c r="AD67" s="38" t="inlineStr"/>
       <c r="AE67" s="38" t="inlineStr">
         <is>
-          <t>DRB102 64 = 'spare (size 16)'</t>
+          <t>DRB102 63 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF67" s="38" t="inlineStr">
@@ -8077,7 +8121,7 @@
         </is>
       </c>
       <c r="H68" s="41" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I68" s="42" t="inlineStr">
         <is>
@@ -8093,12 +8137,12 @@
       <c r="P68" s="45" t="inlineStr"/>
       <c r="Q68" s="46" t="inlineStr">
         <is>
-          <t>DRB102.65</t>
+          <t>DRB102.64</t>
         </is>
       </c>
       <c r="R68" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 65)</t>
+          <t>spare (DRB102 64)</t>
         </is>
       </c>
       <c r="S68" s="48" t="inlineStr"/>
@@ -8115,7 +8159,7 @@
       <c r="AD68" s="54" t="inlineStr"/>
       <c r="AE68" s="54" t="inlineStr">
         <is>
-          <t>DRB102 65 = 'spare (size 16)'</t>
+          <t>DRB102 64 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF68" s="54" t="inlineStr">
@@ -8150,7 +8194,7 @@
         </is>
       </c>
       <c r="H69" s="25" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
@@ -8166,12 +8210,12 @@
       <c r="P69" s="29" t="inlineStr"/>
       <c r="Q69" s="30" t="inlineStr">
         <is>
-          <t>DRB102.66</t>
+          <t>DRB102.65</t>
         </is>
       </c>
       <c r="R69" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 66)</t>
+          <t>spare (DRB102 65)</t>
         </is>
       </c>
       <c r="S69" s="32" t="inlineStr"/>
@@ -8188,7 +8232,7 @@
       <c r="AD69" s="38" t="inlineStr"/>
       <c r="AE69" s="38" t="inlineStr">
         <is>
-          <t>DRB102 66 = 'spare (size 16)'</t>
+          <t>DRB102 65 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF69" s="38" t="inlineStr">
@@ -8223,7 +8267,7 @@
         </is>
       </c>
       <c r="H70" s="41" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I70" s="42" t="inlineStr">
         <is>
@@ -8239,12 +8283,12 @@
       <c r="P70" s="45" t="inlineStr"/>
       <c r="Q70" s="46" t="inlineStr">
         <is>
-          <t>DRB102.67</t>
+          <t>DRB102.66</t>
         </is>
       </c>
       <c r="R70" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 67)</t>
+          <t>spare (DRB102 66)</t>
         </is>
       </c>
       <c r="S70" s="48" t="inlineStr"/>
@@ -8261,7 +8305,7 @@
       <c r="AD70" s="54" t="inlineStr"/>
       <c r="AE70" s="54" t="inlineStr">
         <is>
-          <t>DRB102 67 = 'spare (size 16)'</t>
+          <t>DRB102 66 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF70" s="54" t="inlineStr">
@@ -8296,7 +8340,7 @@
         </is>
       </c>
       <c r="H71" s="25" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
@@ -8312,12 +8356,12 @@
       <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>DRB102.68</t>
+          <t>DRB102.67</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 68)</t>
+          <t>spare (DRB102 67)</t>
         </is>
       </c>
       <c r="S71" s="32" t="inlineStr"/>
@@ -8334,7 +8378,7 @@
       <c r="AD71" s="38" t="inlineStr"/>
       <c r="AE71" s="38" t="inlineStr">
         <is>
-          <t>DRB102 68 = 'spare (size 16)'</t>
+          <t>DRB102 67 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF71" s="38" t="inlineStr">
@@ -8369,7 +8413,7 @@
         </is>
       </c>
       <c r="H72" s="41" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I72" s="42" t="inlineStr">
         <is>
@@ -8385,12 +8429,12 @@
       <c r="P72" s="45" t="inlineStr"/>
       <c r="Q72" s="46" t="inlineStr">
         <is>
-          <t>DRB102.69</t>
+          <t>DRB102.68</t>
         </is>
       </c>
       <c r="R72" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 69)</t>
+          <t>spare (DRB102 68)</t>
         </is>
       </c>
       <c r="S72" s="48" t="inlineStr"/>
@@ -8407,7 +8451,7 @@
       <c r="AD72" s="54" t="inlineStr"/>
       <c r="AE72" s="54" t="inlineStr">
         <is>
-          <t>DRB102 69 = 'spare (size 16)'</t>
+          <t>DRB102 68 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF72" s="54" t="inlineStr">
@@ -8442,7 +8486,7 @@
         </is>
       </c>
       <c r="H73" s="25" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I73" s="26" t="inlineStr">
         <is>
@@ -8458,12 +8502,12 @@
       <c r="P73" s="29" t="inlineStr"/>
       <c r="Q73" s="30" t="inlineStr">
         <is>
-          <t>DRB102.70</t>
+          <t>DRB102.69</t>
         </is>
       </c>
       <c r="R73" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 70)</t>
+          <t>spare (DRB102 69)</t>
         </is>
       </c>
       <c r="S73" s="32" t="inlineStr"/>
@@ -8480,7 +8524,7 @@
       <c r="AD73" s="38" t="inlineStr"/>
       <c r="AE73" s="38" t="inlineStr">
         <is>
-          <t>DRB102 70 = 'spare (size 16)'</t>
+          <t>DRB102 69 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF73" s="38" t="inlineStr">
@@ -8515,7 +8559,7 @@
         </is>
       </c>
       <c r="H74" s="41" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="I74" s="42" t="inlineStr">
         <is>
@@ -8531,12 +8575,12 @@
       <c r="P74" s="45" t="inlineStr"/>
       <c r="Q74" s="46" t="inlineStr">
         <is>
-          <t>DRB102.79</t>
+          <t>DRB102.70</t>
         </is>
       </c>
       <c r="R74" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 79)</t>
+          <t>spare (DRB102 70)</t>
         </is>
       </c>
       <c r="S74" s="48" t="inlineStr"/>
@@ -8553,7 +8597,7 @@
       <c r="AD74" s="54" t="inlineStr"/>
       <c r="AE74" s="54" t="inlineStr">
         <is>
-          <t>DRB102 79 = 'spare (size 16)'</t>
+          <t>DRB102 70 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF74" s="54" t="inlineStr">
@@ -8588,7 +8632,7 @@
         </is>
       </c>
       <c r="H75" s="25" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I75" s="26" t="inlineStr">
         <is>
@@ -8604,12 +8648,12 @@
       <c r="P75" s="29" t="inlineStr"/>
       <c r="Q75" s="30" t="inlineStr">
         <is>
-          <t>DRB102.80</t>
+          <t>DRB102.79</t>
         </is>
       </c>
       <c r="R75" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 80)</t>
+          <t>spare (DRB102 79)</t>
         </is>
       </c>
       <c r="S75" s="32" t="inlineStr"/>
@@ -8626,7 +8670,7 @@
       <c r="AD75" s="38" t="inlineStr"/>
       <c r="AE75" s="38" t="inlineStr">
         <is>
-          <t>DRB102 80 = 'spare (size 16)'</t>
+          <t>DRB102 79 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF75" s="38" t="inlineStr">
@@ -8661,7 +8705,7 @@
         </is>
       </c>
       <c r="H76" s="41" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I76" s="42" t="inlineStr">
         <is>
@@ -8677,12 +8721,12 @@
       <c r="P76" s="45" t="inlineStr"/>
       <c r="Q76" s="46" t="inlineStr">
         <is>
-          <t>DRB102.81</t>
+          <t>DRB102.80</t>
         </is>
       </c>
       <c r="R76" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 81)</t>
+          <t>spare (DRB102 80)</t>
         </is>
       </c>
       <c r="S76" s="48" t="inlineStr"/>
@@ -8699,7 +8743,7 @@
       <c r="AD76" s="54" t="inlineStr"/>
       <c r="AE76" s="54" t="inlineStr">
         <is>
-          <t>DRB102 81 = 'spare (size 16)'</t>
+          <t>DRB102 80 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF76" s="54" t="inlineStr">
@@ -8734,7 +8778,7 @@
         </is>
       </c>
       <c r="H77" s="25" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I77" s="26" t="inlineStr">
         <is>
@@ -8750,12 +8794,12 @@
       <c r="P77" s="29" t="inlineStr"/>
       <c r="Q77" s="30" t="inlineStr">
         <is>
-          <t>DRB102.82</t>
+          <t>DRB102.81</t>
         </is>
       </c>
       <c r="R77" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 82)</t>
+          <t>spare (DRB102 81)</t>
         </is>
       </c>
       <c r="S77" s="32" t="inlineStr"/>
@@ -8772,7 +8816,7 @@
       <c r="AD77" s="38" t="inlineStr"/>
       <c r="AE77" s="38" t="inlineStr">
         <is>
-          <t>DRB102 82 = 'spare (size 16)'</t>
+          <t>DRB102 81 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF77" s="38" t="inlineStr">
@@ -8807,7 +8851,7 @@
         </is>
       </c>
       <c r="H78" s="41" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="I78" s="42" t="inlineStr">
         <is>
@@ -8823,12 +8867,12 @@
       <c r="P78" s="45" t="inlineStr"/>
       <c r="Q78" s="46" t="inlineStr">
         <is>
-          <t>DRB102.97</t>
+          <t>DRB102.82</t>
         </is>
       </c>
       <c r="R78" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 97)</t>
+          <t>spare (DRB102 82)</t>
         </is>
       </c>
       <c r="S78" s="48" t="inlineStr"/>
@@ -8845,7 +8889,7 @@
       <c r="AD78" s="54" t="inlineStr"/>
       <c r="AE78" s="54" t="inlineStr">
         <is>
-          <t>DRB102 97 = 'spare (size 12)'</t>
+          <t>DRB102 82 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF78" s="54" t="inlineStr">
@@ -8880,7 +8924,7 @@
         </is>
       </c>
       <c r="H79" s="25" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I79" s="26" t="inlineStr">
         <is>
@@ -8896,12 +8940,12 @@
       <c r="P79" s="29" t="inlineStr"/>
       <c r="Q79" s="30" t="inlineStr">
         <is>
-          <t>DRB102.98</t>
+          <t>DRB102.97</t>
         </is>
       </c>
       <c r="R79" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 98)</t>
+          <t>spare (DRB102 97)</t>
         </is>
       </c>
       <c r="S79" s="32" t="inlineStr"/>
@@ -8918,7 +8962,7 @@
       <c r="AD79" s="38" t="inlineStr"/>
       <c r="AE79" s="38" t="inlineStr">
         <is>
-          <t>DRB102 98 = 'spare (size 12)'</t>
+          <t>DRB102 97 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF79" s="38" t="inlineStr">
@@ -8953,7 +8997,7 @@
         </is>
       </c>
       <c r="H80" s="41" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I80" s="42" t="inlineStr">
         <is>
@@ -8969,12 +9013,12 @@
       <c r="P80" s="45" t="inlineStr"/>
       <c r="Q80" s="46" t="inlineStr">
         <is>
-          <t>DRB102.99</t>
+          <t>DRB102.98</t>
         </is>
       </c>
       <c r="R80" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 99)</t>
+          <t>spare (DRB102 98)</t>
         </is>
       </c>
       <c r="S80" s="48" t="inlineStr"/>
@@ -8991,7 +9035,7 @@
       <c r="AD80" s="54" t="inlineStr"/>
       <c r="AE80" s="54" t="inlineStr">
         <is>
-          <t>DRB102 99 = 'spare (size 12)'</t>
+          <t>DRB102 98 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF80" s="54" t="inlineStr">
@@ -9026,7 +9070,7 @@
         </is>
       </c>
       <c r="H81" s="25" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I81" s="26" t="inlineStr">
         <is>
@@ -9042,12 +9086,12 @@
       <c r="P81" s="29" t="inlineStr"/>
       <c r="Q81" s="30" t="inlineStr">
         <is>
-          <t>DRB102.100</t>
+          <t>DRB102.99</t>
         </is>
       </c>
       <c r="R81" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 100)</t>
+          <t>spare (DRB102 99)</t>
         </is>
       </c>
       <c r="S81" s="32" t="inlineStr"/>
@@ -9064,7 +9108,7 @@
       <c r="AD81" s="38" t="inlineStr"/>
       <c r="AE81" s="38" t="inlineStr">
         <is>
-          <t>DRB102 100 = 'spare (size 12)'</t>
+          <t>DRB102 99 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF81" s="38" t="inlineStr">
@@ -9099,7 +9143,7 @@
         </is>
       </c>
       <c r="H82" s="41" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I82" s="42" t="inlineStr">
         <is>
@@ -9115,12 +9159,12 @@
       <c r="P82" s="45" t="inlineStr"/>
       <c r="Q82" s="46" t="inlineStr">
         <is>
-          <t>DRB102.101</t>
+          <t>DRB102.100</t>
         </is>
       </c>
       <c r="R82" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 101)</t>
+          <t>spare (DRB102 100)</t>
         </is>
       </c>
       <c r="S82" s="48" t="inlineStr"/>
@@ -9137,7 +9181,7 @@
       <c r="AD82" s="54" t="inlineStr"/>
       <c r="AE82" s="54" t="inlineStr">
         <is>
-          <t>DRB102 101 = 'spare (size 12)'</t>
+          <t>DRB102 100 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF82" s="54" t="inlineStr">
@@ -9172,7 +9216,7 @@
         </is>
       </c>
       <c r="H83" s="25" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I83" s="26" t="inlineStr">
         <is>
@@ -9188,12 +9232,12 @@
       <c r="P83" s="29" t="inlineStr"/>
       <c r="Q83" s="30" t="inlineStr">
         <is>
-          <t>DRB102.102</t>
+          <t>DRB102.101</t>
         </is>
       </c>
       <c r="R83" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 102)</t>
+          <t>spare (DRB102 101)</t>
         </is>
       </c>
       <c r="S83" s="32" t="inlineStr"/>
@@ -9210,7 +9254,7 @@
       <c r="AD83" s="38" t="inlineStr"/>
       <c r="AE83" s="38" t="inlineStr">
         <is>
-          <t>DRB102 102 = 'spare (size 12)'</t>
+          <t>DRB102 101 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF83" s="38" t="inlineStr">
@@ -9236,22 +9280,20 @@
       </c>
       <c r="F84" s="41" t="inlineStr">
         <is>
-          <t>ecu_b</t>
+          <t>bh_b_fw</t>
         </is>
       </c>
       <c r="G84" s="42" t="inlineStr">
         <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H84" s="41" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
+          <t>BH-B (firewall bulkhead DRB102, RH)</t>
+        </is>
+      </c>
+      <c r="H84" s="41" t="n">
+        <v>102</v>
       </c>
       <c r="I84" s="42" t="inlineStr">
         <is>
-          <t>spare, not used</t>
+          <t>spare, sealing plug</t>
         </is>
       </c>
       <c r="J84" s="42" t="inlineStr"/>
@@ -9263,12 +9305,12 @@
       <c r="P84" s="45" t="inlineStr"/>
       <c r="Q84" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B1</t>
+          <t>DRB102.102</t>
         </is>
       </c>
       <c r="R84" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-B B1)</t>
+          <t>spare (DRB102 102)</t>
         </is>
       </c>
       <c r="S84" s="48" t="inlineStr"/>
@@ -9283,7 +9325,11 @@
       <c r="AB84" s="53" t="inlineStr"/>
       <c r="AC84" s="54" t="inlineStr"/>
       <c r="AD84" s="54" t="inlineStr"/>
-      <c r="AE84" s="54" t="inlineStr"/>
+      <c r="AE84" s="54" t="inlineStr">
+        <is>
+          <t>DRB102 102 = 'spare (size 12)'</t>
+        </is>
+      </c>
       <c r="AF84" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -9317,7 +9363,7 @@
       </c>
       <c r="H85" s="25" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="I85" s="26" t="inlineStr">
@@ -9334,12 +9380,12 @@
       <c r="P85" s="29" t="inlineStr"/>
       <c r="Q85" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B2</t>
+          <t>ECU-B.B1</t>
         </is>
       </c>
       <c r="R85" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-B B2)</t>
+          <t>spare (ECU-B B1)</t>
         </is>
       </c>
       <c r="S85" s="32" t="inlineStr"/>
@@ -9388,7 +9434,7 @@
       </c>
       <c r="H86" s="41" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="I86" s="42" t="inlineStr">
@@ -9405,12 +9451,12 @@
       <c r="P86" s="45" t="inlineStr"/>
       <c r="Q86" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B3</t>
+          <t>ECU-B.B2</t>
         </is>
       </c>
       <c r="R86" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-B B3)</t>
+          <t>spare (ECU-B B2)</t>
         </is>
       </c>
       <c r="S86" s="48" t="inlineStr"/>
@@ -9459,7 +9505,7 @@
       </c>
       <c r="H87" s="25" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="I87" s="26" t="inlineStr">
@@ -9476,12 +9522,12 @@
       <c r="P87" s="29" t="inlineStr"/>
       <c r="Q87" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B4</t>
+          <t>ECU-B.B3</t>
         </is>
       </c>
       <c r="R87" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-B B4)</t>
+          <t>spare (ECU-B B3)</t>
         </is>
       </c>
       <c r="S87" s="32" t="inlineStr"/>
@@ -9530,7 +9576,7 @@
       </c>
       <c r="H88" s="41" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="I88" s="42" t="inlineStr">
@@ -9547,12 +9593,12 @@
       <c r="P88" s="45" t="inlineStr"/>
       <c r="Q88" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B8</t>
+          <t>ECU-B.B4</t>
         </is>
       </c>
       <c r="R88" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-B B8)</t>
+          <t>spare (ECU-B B4)</t>
         </is>
       </c>
       <c r="S88" s="48" t="inlineStr"/>
@@ -9601,7 +9647,7 @@
       </c>
       <c r="H89" s="25" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B8</t>
         </is>
       </c>
       <c r="I89" s="26" t="inlineStr">
@@ -9618,12 +9664,12 @@
       <c r="P89" s="29" t="inlineStr"/>
       <c r="Q89" s="30" t="inlineStr">
         <is>
-          <t>ECU-B.B11</t>
+          <t>ECU-B.B8</t>
         </is>
       </c>
       <c r="R89" s="31" t="inlineStr">
         <is>
-          <t>spare (ECU-B B11)</t>
+          <t>spare (ECU-B B8)</t>
         </is>
       </c>
       <c r="S89" s="32" t="inlineStr"/>
@@ -9672,7 +9718,7 @@
       </c>
       <c r="H90" s="41" t="inlineStr">
         <is>
-          <t>B14</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="I90" s="42" t="inlineStr">
@@ -9689,12 +9735,12 @@
       <c r="P90" s="45" t="inlineStr"/>
       <c r="Q90" s="46" t="inlineStr">
         <is>
-          <t>ECU-B.B14</t>
+          <t>ECU-B.B11</t>
         </is>
       </c>
       <c r="R90" s="47" t="inlineStr">
         <is>
-          <t>spare (ECU-B B14)</t>
+          <t>spare (ECU-B B11)</t>
         </is>
       </c>
       <c r="S90" s="48" t="inlineStr"/>
@@ -9733,20 +9779,22 @@
       </c>
       <c r="F91" s="25" t="inlineStr">
         <is>
-          <t>ix_ws_rear_p</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G91" s="26" t="inlineStr">
         <is>
-          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
-        </is>
-      </c>
-      <c r="H91" s="25" t="n">
-        <v>6</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H91" s="25" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
       </c>
       <c r="I91" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J91" s="26" t="inlineStr"/>
@@ -9758,12 +9806,12 @@
       <c r="P91" s="29" t="inlineStr"/>
       <c r="Q91" s="30" t="inlineStr">
         <is>
-          <t>ix_ws_rear_p.6</t>
+          <t>ECU-B.B14</t>
         </is>
       </c>
       <c r="R91" s="31" t="inlineStr">
         <is>
-          <t>spare (ix_ws_rear_p 6)</t>
+          <t>spare (ECU-B B14)</t>
         </is>
       </c>
       <c r="S91" s="32" t="inlineStr"/>
@@ -9786,8 +9834,77 @@
       </c>
       <c r="AG91" s="38" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" s="39" t="inlineStr"/>
+      <c r="B92" s="39" t="inlineStr"/>
+      <c r="C92" s="39" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
+      <c r="D92" s="39" t="inlineStr"/>
+      <c r="E92" s="40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="F92" s="41" t="inlineStr">
+        <is>
+          <t>ix_ws_rear_p</t>
+        </is>
+      </c>
+      <c r="G92" s="42" t="inlineStr">
+        <is>
+          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
+        </is>
+      </c>
+      <c r="H92" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="I92" s="42" t="inlineStr">
+        <is>
+          <t>spare, sealing plug</t>
+        </is>
+      </c>
+      <c r="J92" s="42" t="inlineStr"/>
+      <c r="K92" s="43" t="inlineStr"/>
+      <c r="L92" s="44" t="inlineStr"/>
+      <c r="M92" s="45" t="inlineStr"/>
+      <c r="N92" s="44" t="inlineStr"/>
+      <c r="O92" s="45" t="inlineStr"/>
+      <c r="P92" s="45" t="inlineStr"/>
+      <c r="Q92" s="46" t="inlineStr">
+        <is>
+          <t>ix_ws_rear_p.6</t>
+        </is>
+      </c>
+      <c r="R92" s="47" t="inlineStr">
+        <is>
+          <t>spare (ix_ws_rear_p 6)</t>
+        </is>
+      </c>
+      <c r="S92" s="48" t="inlineStr"/>
+      <c r="T92" s="48" t="inlineStr"/>
+      <c r="U92" s="49" t="inlineStr"/>
+      <c r="V92" s="50" t="inlineStr"/>
+      <c r="W92" s="50" t="inlineStr"/>
+      <c r="X92" s="50" t="inlineStr"/>
+      <c r="Y92" s="50" t="inlineStr"/>
+      <c r="Z92" s="51" t="inlineStr"/>
+      <c r="AA92" s="52" t="inlineStr"/>
+      <c r="AB92" s="53" t="inlineStr"/>
+      <c r="AC92" s="54" t="inlineStr"/>
+      <c r="AD92" s="54" t="inlineStr"/>
+      <c r="AE92" s="54" t="inlineStr"/>
+      <c r="AF92" s="54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AG92" s="54" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AG91"/>
+  <autoFilter ref="A2:AG92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -9799,16 +9916,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
@@ -10027,14 +10144,14 @@
       </c>
       <c r="G4" s="48" t="inlineStr">
         <is>
-          <t>20+20+20+20 + shield</t>
+          <t>20+20+20+20+20</t>
         </is>
       </c>
       <c r="H4" s="48" t="n">
-        <v>4088</v>
+        <v>5110</v>
       </c>
       <c r="I4" s="48" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J4" s="58" t="inlineStr">
         <is>
@@ -10388,8 +10505,64 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>sp_shield_b_wsr</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="inlineStr">
+        <is>
+          <t>At the rear WS inline - SP-SHIELD-B-WSR: rear wheel-speed drains</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B-cabin</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>ECU-B.B17</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>Screen B (ECU B17, SHIELD_B)</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>20 + shield</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>1022</v>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" s="56" t="inlineStr">
+        <is>
+          <t>SPLICE, SOLDERED, ADHESIVE HEATSHRINK OVER</t>
+        </is>
+      </c>
+      <c r="K11" s="36" t="inlineStr">
+        <is>
+          <t>At the rear WS inline (layout node bp_1020)</t>
+        </is>
+      </c>
+      <c r="L11" s="38" t="inlineStr">
+        <is>
+          <t>node of the wire list (SoT)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:L10"/>
+  <autoFilter ref="A2:L11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/docs/harness/wirelist/B-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/B-cabin-wirelist.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Mates" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Wire list'!$A$2:$AG$72</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wire list'!$1:$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Splices'!$A$2:$L$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Splices'!$1:$2</definedName>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AG92"/>
+  <dimension ref="A1:AG72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="H3" s="25" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I3" s="26" t="inlineStr">
         <is>
@@ -1182,12 +1182,12 @@
       <c r="P3" s="29" t="inlineStr"/>
       <c r="Q3" s="30" t="inlineStr">
         <is>
-          <t>DRB102.76</t>
+          <t>DRB102.78</t>
         </is>
       </c>
       <c r="R3" s="31" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out (DRB102 76)</t>
+          <t>Reverse sw +12 V out (DRB102 78)</t>
         </is>
       </c>
       <c r="S3" s="32" t="inlineStr">
@@ -1222,7 +1222,7 @@
       <c r="AD3" s="38" t="inlineStr"/>
       <c r="AE3" s="38" t="inlineStr">
         <is>
-          <t>DRB102 76 = section B c12 'Back-up switch B1 pin 1 out (+12V in reverse) -&gt; r'; splice sp_rev_sw: node of the wire list (SoT)</t>
+          <t>DRB102 78 = loom B c78 'Reverse sw +12 V out'; splice sp_rev_sw: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF3" s="38" t="inlineStr">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="H4" s="41" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I4" s="42" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       <c r="AD4" s="54" t="inlineStr"/>
       <c r="AE4" s="54" t="inlineStr">
         <is>
-          <t>DRB102 84 = section B c17 'Knock 1 SIG- (to Gnd Out B22)'; splice sp_gnd_bhb: node of the wire list (SoT)</t>
+          <t>DRB102 72 = loom B c72 'Knock sensor (-)'; splice sp_gnd_bhb: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF4" s="54" t="inlineStr">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="H5" s="25" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
       <c r="AD5" s="38" t="inlineStr"/>
       <c r="AE5" s="38" t="inlineStr">
         <is>
-          <t>DRB102 85 = section B c18 'Knock 1 screen'; splice sp_shield_b: node of the wire list (SoT)</t>
+          <t>DRB102 73 = loom B c73 'Knock sensor shield'; splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF5" s="38" t="inlineStr">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="H6" s="41" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
       <c r="AD6" s="54" t="inlineStr"/>
       <c r="AE6" s="54" t="inlineStr">
         <is>
-          <t>DRB102 88 = section B c22 'ETB motor screen (to B17)'; splice sp_shield_b: node of the wire list (SoT)</t>
+          <t>DRB102 50 = loom B c50 'ETB motor shield'; splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF6" s="54" t="inlineStr">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="H7" s="25" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="I7" s="26" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
       <c r="AD7" s="38" t="inlineStr"/>
       <c r="AE7" s="38" t="inlineStr">
         <is>
-          <t>DRB102 89 = section B c15 'Gearbox VSS signal (ECU B29, DI 8)'; channels.csv ecu_b B29 DI 8 (DI8_VSS)</t>
+          <t>DRB102 68 = loom B c68 'ECU-B B29'; channels.csv ecu_b B29 DI 8 (DI8_VSS)</t>
         </is>
       </c>
       <c r="AF7" s="38" t="inlineStr">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="H8" s="41" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
       <c r="AD8" s="54" t="inlineStr"/>
       <c r="AE8" s="54" t="inlineStr">
         <is>
-          <t>DRB102 91 = section B c23 'Gearbox VSS screen (to B17)'; splice sp_shield_b: node of the wire list (SoT)</t>
+          <t>DRB102 69 = loom B c69 'Gearbox speed shield'; splice sp_shield_b: node of the wire list (SoT)</t>
         </is>
       </c>
       <c r="AF8" s="54" t="inlineStr">
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="N9" s="28" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="O9" s="29" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
       <c r="AD9" s="38" t="inlineStr"/>
       <c r="AE9" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B6 Temp 3 (TEMP3_OIL_T); DRB102 74 = section B c10 'ECU-B B6'</t>
+          <t>channels.csv ecu_b B6 Temp 3 (TEMP3_OIL_T); DRB102 61 = loom B c61 'ECU-B B6'</t>
         </is>
       </c>
       <c r="AF9" s="38" t="inlineStr">
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="N10" s="44" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="O10" s="45" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
       <c r="AD10" s="54" t="inlineStr"/>
       <c r="AE10" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B7 Temp 4 (TEMP4_CHG_IAT); DRB102 75 = section B c11 'ECU-B B7'</t>
+          <t>channels.csv ecu_b B7 Temp 4 (TEMP4_CHG_IAT); DRB102 59 = loom B c59 'ECU-B B7'</t>
         </is>
       </c>
       <c r="AF10" s="54" t="inlineStr">
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="N11" s="28" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="O11" s="29" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
       <c r="AD11" s="38" t="inlineStr"/>
       <c r="AE11" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B9 Knock 1 (KNOCK1_SIG); DRB102 83 = section B c16 'Knock 1 SIG+ (ECU B9)'</t>
+          <t>channels.csv ecu_b B9 Knock 1 (KNOCK1_SIG); DRB102 71 = loom B c71 'ECU-B B9'</t>
         </is>
       </c>
       <c r="AF11" s="38" t="inlineStr">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="N14" s="44" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="O14" s="45" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       <c r="AD14" s="54" t="inlineStr"/>
       <c r="AE14" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B15 An Volt 6 (AV6_OIL_P); DRB102 71 = section B c7 'ECU-B B15'</t>
+          <t>channels.csv ecu_b B15 An Volt 6 (AV6_OIL_P); DRB102 28 = loom B c28 'ECU-B B15'</t>
         </is>
       </c>
       <c r="AF14" s="54" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="N15" s="28" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="O15" s="29" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
       <c r="AD15" s="38" t="inlineStr"/>
       <c r="AE15" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B16 An Volt 7 (AV7_FUEL_P); DRB102 72 = section B c8 'ECU-B B16'</t>
+          <t>channels.csv ecu_b B16 An Volt 7 (AV7_FUEL_P); DRB102 14 = loom B c14 'ECU-B B16'</t>
         </is>
       </c>
       <c r="AF15" s="38" t="inlineStr">
@@ -2669,7 +2669,7 @@
         </is>
       </c>
       <c r="N16" s="44" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="O16" s="45" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
       <c r="AD16" s="54" t="inlineStr"/>
       <c r="AE16" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B18 Aux 9 (AUX9_ETB_MP); DRB102 86 = section B c5 'ETB motor + (Aux 9, B18)'</t>
+          <t>channels.csv ecu_b B18 Aux 9 (AUX9_ETB_MP); DRB102 45 = loom B c45 'ECU-B B18'</t>
         </is>
       </c>
       <c r="AF16" s="54" t="inlineStr">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="N18" s="44" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="O18" s="45" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
       <c r="AD18" s="54" t="inlineStr"/>
       <c r="AE18" s="54" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B23 An Volt 8 (AV8_CLNT_P); DRB102 73 = section B c9 'ECU-B B23'</t>
+          <t>channels.csv ecu_b B23 An Volt 8 (AV8_CLNT_P); DRB102 26 = loom B c26 'ECU-B B23'</t>
         </is>
       </c>
       <c r="AF18" s="54" t="inlineStr">
@@ -3012,7 +3012,7 @@
         </is>
       </c>
       <c r="N19" s="28" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="O19" s="29" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
       <c r="AD19" s="38" t="inlineStr"/>
       <c r="AE19" s="38" t="inlineStr">
         <is>
-          <t>channels.csv ecu_b B26 Aux 10 (AUX10_ETB_MN); DRB102 87 = section B c6 'ETB motor - (Aux 10, B26)'</t>
+          <t>channels.csv ecu_b B26 Aux 10 (AUX10_ETB_MN); DRB102 46 = loom B c46 'ECU-B B26'</t>
         </is>
       </c>
       <c r="AF19" s="38" t="inlineStr">
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="N38" s="44" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="O38" s="45" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
       <c r="AD38" s="54" t="inlineStr"/>
       <c r="AE38" s="54" t="inlineStr">
         <is>
-          <t>splice sp_canh: node of the wire list (SoT); DRB102 92 = section B c13 'CAN H to Link CAN-Lambda (ST185-CAN)'</t>
+          <t>splice sp_canh: node of the wire list (SoT); DRB102 79 = loom B c79 'CAN H to CAN-Lambda'</t>
         </is>
       </c>
       <c r="AF38" s="54" t="inlineStr">
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="N39" s="28" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="O39" s="29" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
       <c r="AD39" s="38" t="inlineStr"/>
       <c r="AE39" s="38" t="inlineStr">
         <is>
-          <t>splice sp_canl: node of the wire list (SoT); DRB102 93 = section B c14 'CAN L to Link CAN-Lambda (ST185-CAN)'</t>
+          <t>splice sp_canl: node of the wire list (SoT); DRB102 80 = loom B c80 'CAN L to CAN-Lambda'</t>
         </is>
       </c>
       <c r="AF39" s="38" t="inlineStr">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="N43" s="28" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="O43" s="29" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
       <c r="AD43" s="38" t="inlineStr"/>
       <c r="AE43" s="38" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb: node of the wire list (SoT); DRB102 77 = section B c19 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
+          <t>splice sp_gnd_bhb: node of the wire list (SoT); DRB102 29 = loom B c29 'Gnd oil/clnt/temps'</t>
         </is>
       </c>
       <c r="AF43" s="38" t="inlineStr">
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="N44" s="44" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="O44" s="45" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
       <c r="AD44" s="54" t="inlineStr"/>
       <c r="AE44" s="54" t="inlineStr">
         <is>
-          <t>splice sp_gnd_bhb: node of the wire list (SoT); DRB102 78 = section B c21 'Gnd Out (ECU B22) to B engine sensors (bulkhead sp'</t>
+          <t>splice sp_gnd_bhb: node of the wire list (SoT); DRB102 15 = loom B c15 'Gnd fuel press + VSS'</t>
         </is>
       </c>
       <c r="AF44" s="54" t="inlineStr">
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="N46" s="44" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O46" s="45" t="inlineStr">
         <is>
@@ -6157,12 +6157,12 @@
       <c r="P46" s="45" t="inlineStr"/>
       <c r="Q46" s="46" t="inlineStr">
         <is>
-          <t>DRB102.62</t>
+          <t>DRB102.77</t>
         </is>
       </c>
       <c r="R46" s="47" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in (DRB102 62)</t>
+          <t>Back-up sw +12 V in (DRB102 77)</t>
         </is>
       </c>
       <c r="S46" s="48" t="inlineStr">
@@ -6199,7 +6199,7 @@
       <c r="AD46" s="54" t="inlineStr"/>
       <c r="AE46" s="54" t="inlineStr">
         <is>
-          <t>splice sp_rev_gauge: node of the wire list (SoT); DRB102 62 = section B c25 'Back-up switch B1 pin 2 feed &lt;- J/B No.1 GAUGE 15A'</t>
+          <t>splice sp_rev_gauge: node of the wire list (SoT); DRB102 77 = loom B c77 'Back-up sw +12 V in'</t>
         </is>
       </c>
       <c r="AF46" s="54" t="inlineStr">
@@ -6282,12 +6282,12 @@
       <c r="P47" s="29" t="inlineStr"/>
       <c r="Q47" s="30" t="inlineStr">
         <is>
-          <t>DRB102.76</t>
+          <t>DRB102.78</t>
         </is>
       </c>
       <c r="R47" s="31" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out (DRB102 76)</t>
+          <t>Reverse sw +12 V out (DRB102 78)</t>
         </is>
       </c>
       <c r="S47" s="32" t="inlineStr">
@@ -6407,12 +6407,12 @@
       <c r="P48" s="45" t="inlineStr"/>
       <c r="Q48" s="46" t="inlineStr">
         <is>
-          <t>DRB102.76</t>
+          <t>DRB102.78</t>
         </is>
       </c>
       <c r="R48" s="47" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out (DRB102 76)</t>
+          <t>Reverse sw +12 V out (DRB102 78)</t>
         </is>
       </c>
       <c r="S48" s="48" t="inlineStr">
@@ -6754,7 +6754,7 @@
         </is>
       </c>
       <c r="N51" s="28" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="O51" s="29" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
       <c r="AD51" s="38" t="inlineStr"/>
       <c r="AE51" s="38" t="inlineStr">
         <is>
-          <t>splice sp_can_sh_bh: node of the wire list (SoT); DRB102 94 = section B c24 'CAN-Lambda CAN pair screen (to ECU C1, via the CAN'</t>
+          <t>splice sp_can_sh_bh: node of the wire list (SoT); DRB102 81 = loom B c81 'CAN-Lambda shield'</t>
         </is>
       </c>
       <c r="AF51" s="38" t="inlineStr">
@@ -7163,20 +7163,22 @@
       </c>
       <c r="F55" s="25" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G55" s="26" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H55" s="25" t="n">
-        <v>3</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H55" s="25" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
       </c>
       <c r="I55" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J55" s="26" t="inlineStr"/>
@@ -7188,12 +7190,12 @@
       <c r="P55" s="29" t="inlineStr"/>
       <c r="Q55" s="30" t="inlineStr">
         <is>
-          <t>DRB102.3</t>
+          <t>ECU-B.B1</t>
         </is>
       </c>
       <c r="R55" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 3)</t>
+          <t>spare (ECU-B B1)</t>
         </is>
       </c>
       <c r="S55" s="32" t="inlineStr"/>
@@ -7208,11 +7210,7 @@
       <c r="AB55" s="37" t="inlineStr"/>
       <c r="AC55" s="38" t="inlineStr"/>
       <c r="AD55" s="38" t="inlineStr"/>
-      <c r="AE55" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 3 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE55" s="38" t="inlineStr"/>
       <c r="AF55" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7236,20 +7234,22 @@
       </c>
       <c r="F56" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G56" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H56" s="41" t="n">
-        <v>4</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H56" s="41" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
       </c>
       <c r="I56" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J56" s="42" t="inlineStr"/>
@@ -7261,12 +7261,12 @@
       <c r="P56" s="45" t="inlineStr"/>
       <c r="Q56" s="46" t="inlineStr">
         <is>
-          <t>DRB102.4</t>
+          <t>ECU-B.B2</t>
         </is>
       </c>
       <c r="R56" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 4)</t>
+          <t>spare (ECU-B B2)</t>
         </is>
       </c>
       <c r="S56" s="48" t="inlineStr"/>
@@ -7281,11 +7281,7 @@
       <c r="AB56" s="53" t="inlineStr"/>
       <c r="AC56" s="54" t="inlineStr"/>
       <c r="AD56" s="54" t="inlineStr"/>
-      <c r="AE56" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 4 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE56" s="54" t="inlineStr"/>
       <c r="AF56" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7309,20 +7305,22 @@
       </c>
       <c r="F57" s="25" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G57" s="26" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H57" s="25" t="n">
-        <v>5</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H57" s="25" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
       </c>
       <c r="I57" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J57" s="26" t="inlineStr"/>
@@ -7334,12 +7332,12 @@
       <c r="P57" s="29" t="inlineStr"/>
       <c r="Q57" s="30" t="inlineStr">
         <is>
-          <t>DRB102.5</t>
+          <t>ECU-B.B3</t>
         </is>
       </c>
       <c r="R57" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 5)</t>
+          <t>spare (ECU-B B3)</t>
         </is>
       </c>
       <c r="S57" s="32" t="inlineStr"/>
@@ -7354,11 +7352,7 @@
       <c r="AB57" s="37" t="inlineStr"/>
       <c r="AC57" s="38" t="inlineStr"/>
       <c r="AD57" s="38" t="inlineStr"/>
-      <c r="AE57" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 5 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE57" s="38" t="inlineStr"/>
       <c r="AF57" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7382,20 +7376,22 @@
       </c>
       <c r="F58" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G58" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H58" s="41" t="n">
-        <v>6</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H58" s="41" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
       </c>
       <c r="I58" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J58" s="42" t="inlineStr"/>
@@ -7407,12 +7403,12 @@
       <c r="P58" s="45" t="inlineStr"/>
       <c r="Q58" s="46" t="inlineStr">
         <is>
-          <t>DRB102.6</t>
+          <t>ECU-B.B4</t>
         </is>
       </c>
       <c r="R58" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 6)</t>
+          <t>spare (ECU-B B4)</t>
         </is>
       </c>
       <c r="S58" s="48" t="inlineStr"/>
@@ -7427,11 +7423,7 @@
       <c r="AB58" s="53" t="inlineStr"/>
       <c r="AC58" s="54" t="inlineStr"/>
       <c r="AD58" s="54" t="inlineStr"/>
-      <c r="AE58" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 6 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE58" s="54" t="inlineStr"/>
       <c r="AF58" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7455,20 +7447,22 @@
       </c>
       <c r="F59" s="25" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G59" s="26" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H59" s="25" t="n">
-        <v>7</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H59" s="25" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
       </c>
       <c r="I59" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J59" s="26" t="inlineStr"/>
@@ -7480,12 +7474,12 @@
       <c r="P59" s="29" t="inlineStr"/>
       <c r="Q59" s="30" t="inlineStr">
         <is>
-          <t>DRB102.7</t>
+          <t>ECU-B.B8</t>
         </is>
       </c>
       <c r="R59" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 7)</t>
+          <t>spare (ECU-B B8)</t>
         </is>
       </c>
       <c r="S59" s="32" t="inlineStr"/>
@@ -7500,11 +7494,7 @@
       <c r="AB59" s="37" t="inlineStr"/>
       <c r="AC59" s="38" t="inlineStr"/>
       <c r="AD59" s="38" t="inlineStr"/>
-      <c r="AE59" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 7 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE59" s="38" t="inlineStr"/>
       <c r="AF59" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7528,20 +7518,22 @@
       </c>
       <c r="F60" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G60" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H60" s="41" t="n">
-        <v>8</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H60" s="41" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
       </c>
       <c r="I60" s="42" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J60" s="42" t="inlineStr"/>
@@ -7553,12 +7545,12 @@
       <c r="P60" s="45" t="inlineStr"/>
       <c r="Q60" s="46" t="inlineStr">
         <is>
-          <t>DRB102.8</t>
+          <t>ECU-B.B11</t>
         </is>
       </c>
       <c r="R60" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 8)</t>
+          <t>spare (ECU-B B11)</t>
         </is>
       </c>
       <c r="S60" s="48" t="inlineStr"/>
@@ -7573,11 +7565,7 @@
       <c r="AB60" s="53" t="inlineStr"/>
       <c r="AC60" s="54" t="inlineStr"/>
       <c r="AD60" s="54" t="inlineStr"/>
-      <c r="AE60" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 8 = 'spare (size 12)'</t>
-        </is>
-      </c>
+      <c r="AE60" s="54" t="inlineStr"/>
       <c r="AF60" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7601,20 +7589,22 @@
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ecu_b</t>
         </is>
       </c>
       <c r="G61" s="26" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H61" s="25" t="n">
-        <v>43</v>
+          <t>ECU-B (Link G4X plug B, centre dash)</t>
+        </is>
+      </c>
+      <c r="H61" s="25" t="inlineStr">
+        <is>
+          <t>B14</t>
+        </is>
       </c>
       <c r="I61" s="26" t="inlineStr">
         <is>
-          <t>spare, sealing plug</t>
+          <t>spare, not used</t>
         </is>
       </c>
       <c r="J61" s="26" t="inlineStr"/>
@@ -7626,12 +7616,12 @@
       <c r="P61" s="29" t="inlineStr"/>
       <c r="Q61" s="30" t="inlineStr">
         <is>
-          <t>DRB102.43</t>
+          <t>ECU-B.B14</t>
         </is>
       </c>
       <c r="R61" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 43)</t>
+          <t>spare (ECU-B B14)</t>
         </is>
       </c>
       <c r="S61" s="32" t="inlineStr"/>
@@ -7646,11 +7636,7 @@
       <c r="AB61" s="37" t="inlineStr"/>
       <c r="AC61" s="38" t="inlineStr"/>
       <c r="AD61" s="38" t="inlineStr"/>
-      <c r="AE61" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 43 = 'spare (size 4)'</t>
-        </is>
-      </c>
+      <c r="AE61" s="38" t="inlineStr"/>
       <c r="AF61" s="38" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7674,16 +7660,16 @@
       </c>
       <c r="F62" s="41" t="inlineStr">
         <is>
-          <t>bh_b_fw</t>
+          <t>ix_ws_rear_p</t>
         </is>
       </c>
       <c r="G62" s="42" t="inlineStr">
         <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
+          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
         </is>
       </c>
       <c r="H62" s="41" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I62" s="42" t="inlineStr">
         <is>
@@ -7699,12 +7685,12 @@
       <c r="P62" s="45" t="inlineStr"/>
       <c r="Q62" s="46" t="inlineStr">
         <is>
-          <t>DRB102.48</t>
+          <t>ix_ws_rear_p.6</t>
         </is>
       </c>
       <c r="R62" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 48)</t>
+          <t>spare (ix_ws_rear_p 6)</t>
         </is>
       </c>
       <c r="S62" s="48" t="inlineStr"/>
@@ -7719,11 +7705,7 @@
       <c r="AB62" s="53" t="inlineStr"/>
       <c r="AC62" s="54" t="inlineStr"/>
       <c r="AD62" s="54" t="inlineStr"/>
-      <c r="AE62" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 48 = 'spare (size 8)'</t>
-        </is>
-      </c>
+      <c r="AE62" s="54" t="inlineStr"/>
       <c r="AF62" s="54" t="inlineStr">
         <is>
           <t>OK</t>
@@ -7756,7 +7738,7 @@
         </is>
       </c>
       <c r="H63" s="25" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I63" s="26" t="inlineStr">
         <is>
@@ -7772,12 +7754,12 @@
       <c r="P63" s="29" t="inlineStr"/>
       <c r="Q63" s="30" t="inlineStr">
         <is>
-          <t>DRB102.49</t>
+          <t>DRB102.51</t>
         </is>
       </c>
       <c r="R63" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 49)</t>
+          <t>spare (DRB102 51)</t>
         </is>
       </c>
       <c r="S63" s="32" t="inlineStr"/>
@@ -7794,7 +7776,7 @@
       <c r="AD63" s="38" t="inlineStr"/>
       <c r="AE63" s="38" t="inlineStr">
         <is>
-          <t>DRB102 49 = 'spare (size 8)'</t>
+          <t>DRB102 51 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF63" s="38" t="inlineStr">
@@ -7829,7 +7811,7 @@
         </is>
       </c>
       <c r="H64" s="41" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I64" s="42" t="inlineStr">
         <is>
@@ -7845,12 +7827,12 @@
       <c r="P64" s="45" t="inlineStr"/>
       <c r="Q64" s="46" t="inlineStr">
         <is>
-          <t>DRB102.54</t>
+          <t>DRB102.60</t>
         </is>
       </c>
       <c r="R64" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 54)</t>
+          <t>spare (DRB102 60)</t>
         </is>
       </c>
       <c r="S64" s="48" t="inlineStr"/>
@@ -7867,7 +7849,7 @@
       <c r="AD64" s="54" t="inlineStr"/>
       <c r="AE64" s="54" t="inlineStr">
         <is>
-          <t>DRB102 54 = 'spare (size 8)'</t>
+          <t>DRB102 60 = 'spare (size 4)'</t>
         </is>
       </c>
       <c r="AF64" s="54" t="inlineStr">
@@ -7902,7 +7884,7 @@
         </is>
       </c>
       <c r="H65" s="25" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I65" s="26" t="inlineStr">
         <is>
@@ -7918,12 +7900,12 @@
       <c r="P65" s="29" t="inlineStr"/>
       <c r="Q65" s="30" t="inlineStr">
         <is>
-          <t>DRB102.55</t>
+          <t>DRB102.62</t>
         </is>
       </c>
       <c r="R65" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 55)</t>
+          <t>spare (DRB102 62)</t>
         </is>
       </c>
       <c r="S65" s="32" t="inlineStr"/>
@@ -7940,7 +7922,7 @@
       <c r="AD65" s="38" t="inlineStr"/>
       <c r="AE65" s="38" t="inlineStr">
         <is>
-          <t>DRB102 55 = 'spare (size 8)'</t>
+          <t>DRB102 62 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF65" s="38" t="inlineStr">
@@ -7975,7 +7957,7 @@
         </is>
       </c>
       <c r="H66" s="41" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="I66" s="42" t="inlineStr">
         <is>
@@ -7991,12 +7973,12 @@
       <c r="P66" s="45" t="inlineStr"/>
       <c r="Q66" s="46" t="inlineStr">
         <is>
-          <t>DRB102.60</t>
+          <t>DRB102.82</t>
         </is>
       </c>
       <c r="R66" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 60)</t>
+          <t>spare (DRB102 82)</t>
         </is>
       </c>
       <c r="S66" s="48" t="inlineStr"/>
@@ -8013,7 +7995,7 @@
       <c r="AD66" s="54" t="inlineStr"/>
       <c r="AE66" s="54" t="inlineStr">
         <is>
-          <t>DRB102 60 = 'spare (size 4)'</t>
+          <t>DRB102 82 = 'spare (size 16)'</t>
         </is>
       </c>
       <c r="AF66" s="54" t="inlineStr">
@@ -8048,7 +8030,7 @@
         </is>
       </c>
       <c r="H67" s="25" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="I67" s="26" t="inlineStr">
         <is>
@@ -8064,12 +8046,12 @@
       <c r="P67" s="29" t="inlineStr"/>
       <c r="Q67" s="30" t="inlineStr">
         <is>
-          <t>DRB102.63</t>
+          <t>DRB102.97</t>
         </is>
       </c>
       <c r="R67" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 63)</t>
+          <t>spare (DRB102 97)</t>
         </is>
       </c>
       <c r="S67" s="32" t="inlineStr"/>
@@ -8086,7 +8068,7 @@
       <c r="AD67" s="38" t="inlineStr"/>
       <c r="AE67" s="38" t="inlineStr">
         <is>
-          <t>DRB102 63 = 'spare (size 16)'</t>
+          <t>DRB102 97 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF67" s="38" t="inlineStr">
@@ -8121,7 +8103,7 @@
         </is>
       </c>
       <c r="H68" s="41" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="I68" s="42" t="inlineStr">
         <is>
@@ -8137,12 +8119,12 @@
       <c r="P68" s="45" t="inlineStr"/>
       <c r="Q68" s="46" t="inlineStr">
         <is>
-          <t>DRB102.64</t>
+          <t>DRB102.98</t>
         </is>
       </c>
       <c r="R68" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 64)</t>
+          <t>spare (DRB102 98)</t>
         </is>
       </c>
       <c r="S68" s="48" t="inlineStr"/>
@@ -8159,7 +8141,7 @@
       <c r="AD68" s="54" t="inlineStr"/>
       <c r="AE68" s="54" t="inlineStr">
         <is>
-          <t>DRB102 64 = 'spare (size 16)'</t>
+          <t>DRB102 98 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF68" s="54" t="inlineStr">
@@ -8194,7 +8176,7 @@
         </is>
       </c>
       <c r="H69" s="25" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="I69" s="26" t="inlineStr">
         <is>
@@ -8210,12 +8192,12 @@
       <c r="P69" s="29" t="inlineStr"/>
       <c r="Q69" s="30" t="inlineStr">
         <is>
-          <t>DRB102.65</t>
+          <t>DRB102.99</t>
         </is>
       </c>
       <c r="R69" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 65)</t>
+          <t>spare (DRB102 99)</t>
         </is>
       </c>
       <c r="S69" s="32" t="inlineStr"/>
@@ -8232,7 +8214,7 @@
       <c r="AD69" s="38" t="inlineStr"/>
       <c r="AE69" s="38" t="inlineStr">
         <is>
-          <t>DRB102 65 = 'spare (size 16)'</t>
+          <t>DRB102 99 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF69" s="38" t="inlineStr">
@@ -8267,7 +8249,7 @@
         </is>
       </c>
       <c r="H70" s="41" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="I70" s="42" t="inlineStr">
         <is>
@@ -8283,12 +8265,12 @@
       <c r="P70" s="45" t="inlineStr"/>
       <c r="Q70" s="46" t="inlineStr">
         <is>
-          <t>DRB102.66</t>
+          <t>DRB102.100</t>
         </is>
       </c>
       <c r="R70" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 66)</t>
+          <t>spare (DRB102 100)</t>
         </is>
       </c>
       <c r="S70" s="48" t="inlineStr"/>
@@ -8305,7 +8287,7 @@
       <c r="AD70" s="54" t="inlineStr"/>
       <c r="AE70" s="54" t="inlineStr">
         <is>
-          <t>DRB102 66 = 'spare (size 16)'</t>
+          <t>DRB102 100 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF70" s="54" t="inlineStr">
@@ -8340,7 +8322,7 @@
         </is>
       </c>
       <c r="H71" s="25" t="n">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="I71" s="26" t="inlineStr">
         <is>
@@ -8356,12 +8338,12 @@
       <c r="P71" s="29" t="inlineStr"/>
       <c r="Q71" s="30" t="inlineStr">
         <is>
-          <t>DRB102.67</t>
+          <t>DRB102.101</t>
         </is>
       </c>
       <c r="R71" s="31" t="inlineStr">
         <is>
-          <t>spare (DRB102 67)</t>
+          <t>spare (DRB102 101)</t>
         </is>
       </c>
       <c r="S71" s="32" t="inlineStr"/>
@@ -8378,7 +8360,7 @@
       <c r="AD71" s="38" t="inlineStr"/>
       <c r="AE71" s="38" t="inlineStr">
         <is>
-          <t>DRB102 67 = 'spare (size 16)'</t>
+          <t>DRB102 101 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF71" s="38" t="inlineStr">
@@ -8413,7 +8395,7 @@
         </is>
       </c>
       <c r="H72" s="41" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="I72" s="42" t="inlineStr">
         <is>
@@ -8429,12 +8411,12 @@
       <c r="P72" s="45" t="inlineStr"/>
       <c r="Q72" s="46" t="inlineStr">
         <is>
-          <t>DRB102.68</t>
+          <t>DRB102.102</t>
         </is>
       </c>
       <c r="R72" s="47" t="inlineStr">
         <is>
-          <t>spare (DRB102 68)</t>
+          <t>spare (DRB102 102)</t>
         </is>
       </c>
       <c r="S72" s="48" t="inlineStr"/>
@@ -8451,7 +8433,7 @@
       <c r="AD72" s="54" t="inlineStr"/>
       <c r="AE72" s="54" t="inlineStr">
         <is>
-          <t>DRB102 68 = 'spare (size 16)'</t>
+          <t>DRB102 102 = 'spare (size 12)'</t>
         </is>
       </c>
       <c r="AF72" s="54" t="inlineStr">
@@ -8461,1450 +8443,8 @@
       </c>
       <c r="AG72" s="54" t="inlineStr"/>
     </row>
-    <row r="73">
-      <c r="A73" s="23" t="inlineStr"/>
-      <c r="B73" s="23" t="inlineStr"/>
-      <c r="C73" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D73" s="23" t="inlineStr"/>
-      <c r="E73" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F73" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G73" s="26" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H73" s="25" t="n">
-        <v>69</v>
-      </c>
-      <c r="I73" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J73" s="26" t="inlineStr"/>
-      <c r="K73" s="27" t="inlineStr"/>
-      <c r="L73" s="28" t="inlineStr"/>
-      <c r="M73" s="29" t="inlineStr"/>
-      <c r="N73" s="28" t="inlineStr"/>
-      <c r="O73" s="29" t="inlineStr"/>
-      <c r="P73" s="29" t="inlineStr"/>
-      <c r="Q73" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.69</t>
-        </is>
-      </c>
-      <c r="R73" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 69)</t>
-        </is>
-      </c>
-      <c r="S73" s="32" t="inlineStr"/>
-      <c r="T73" s="32" t="inlineStr"/>
-      <c r="U73" s="33" t="inlineStr"/>
-      <c r="V73" s="34" t="inlineStr"/>
-      <c r="W73" s="34" t="inlineStr"/>
-      <c r="X73" s="34" t="inlineStr"/>
-      <c r="Y73" s="34" t="inlineStr"/>
-      <c r="Z73" s="35" t="inlineStr"/>
-      <c r="AA73" s="36" t="inlineStr"/>
-      <c r="AB73" s="37" t="inlineStr"/>
-      <c r="AC73" s="38" t="inlineStr"/>
-      <c r="AD73" s="38" t="inlineStr"/>
-      <c r="AE73" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 69 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF73" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG73" s="38" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="39" t="inlineStr"/>
-      <c r="B74" s="39" t="inlineStr"/>
-      <c r="C74" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D74" s="39" t="inlineStr"/>
-      <c r="E74" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F74" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G74" s="42" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H74" s="41" t="n">
-        <v>70</v>
-      </c>
-      <c r="I74" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J74" s="42" t="inlineStr"/>
-      <c r="K74" s="43" t="inlineStr"/>
-      <c r="L74" s="44" t="inlineStr"/>
-      <c r="M74" s="45" t="inlineStr"/>
-      <c r="N74" s="44" t="inlineStr"/>
-      <c r="O74" s="45" t="inlineStr"/>
-      <c r="P74" s="45" t="inlineStr"/>
-      <c r="Q74" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.70</t>
-        </is>
-      </c>
-      <c r="R74" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 70)</t>
-        </is>
-      </c>
-      <c r="S74" s="48" t="inlineStr"/>
-      <c r="T74" s="48" t="inlineStr"/>
-      <c r="U74" s="49" t="inlineStr"/>
-      <c r="V74" s="50" t="inlineStr"/>
-      <c r="W74" s="50" t="inlineStr"/>
-      <c r="X74" s="50" t="inlineStr"/>
-      <c r="Y74" s="50" t="inlineStr"/>
-      <c r="Z74" s="51" t="inlineStr"/>
-      <c r="AA74" s="52" t="inlineStr"/>
-      <c r="AB74" s="53" t="inlineStr"/>
-      <c r="AC74" s="54" t="inlineStr"/>
-      <c r="AD74" s="54" t="inlineStr"/>
-      <c r="AE74" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 70 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF74" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG74" s="54" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="23" t="inlineStr"/>
-      <c r="B75" s="23" t="inlineStr"/>
-      <c r="C75" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D75" s="23" t="inlineStr"/>
-      <c r="E75" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F75" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G75" s="26" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H75" s="25" t="n">
-        <v>79</v>
-      </c>
-      <c r="I75" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J75" s="26" t="inlineStr"/>
-      <c r="K75" s="27" t="inlineStr"/>
-      <c r="L75" s="28" t="inlineStr"/>
-      <c r="M75" s="29" t="inlineStr"/>
-      <c r="N75" s="28" t="inlineStr"/>
-      <c r="O75" s="29" t="inlineStr"/>
-      <c r="P75" s="29" t="inlineStr"/>
-      <c r="Q75" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.79</t>
-        </is>
-      </c>
-      <c r="R75" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 79)</t>
-        </is>
-      </c>
-      <c r="S75" s="32" t="inlineStr"/>
-      <c r="T75" s="32" t="inlineStr"/>
-      <c r="U75" s="33" t="inlineStr"/>
-      <c r="V75" s="34" t="inlineStr"/>
-      <c r="W75" s="34" t="inlineStr"/>
-      <c r="X75" s="34" t="inlineStr"/>
-      <c r="Y75" s="34" t="inlineStr"/>
-      <c r="Z75" s="35" t="inlineStr"/>
-      <c r="AA75" s="36" t="inlineStr"/>
-      <c r="AB75" s="37" t="inlineStr"/>
-      <c r="AC75" s="38" t="inlineStr"/>
-      <c r="AD75" s="38" t="inlineStr"/>
-      <c r="AE75" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 79 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF75" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG75" s="38" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="39" t="inlineStr"/>
-      <c r="B76" s="39" t="inlineStr"/>
-      <c r="C76" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D76" s="39" t="inlineStr"/>
-      <c r="E76" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F76" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G76" s="42" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H76" s="41" t="n">
-        <v>80</v>
-      </c>
-      <c r="I76" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J76" s="42" t="inlineStr"/>
-      <c r="K76" s="43" t="inlineStr"/>
-      <c r="L76" s="44" t="inlineStr"/>
-      <c r="M76" s="45" t="inlineStr"/>
-      <c r="N76" s="44" t="inlineStr"/>
-      <c r="O76" s="45" t="inlineStr"/>
-      <c r="P76" s="45" t="inlineStr"/>
-      <c r="Q76" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.80</t>
-        </is>
-      </c>
-      <c r="R76" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 80)</t>
-        </is>
-      </c>
-      <c r="S76" s="48" t="inlineStr"/>
-      <c r="T76" s="48" t="inlineStr"/>
-      <c r="U76" s="49" t="inlineStr"/>
-      <c r="V76" s="50" t="inlineStr"/>
-      <c r="W76" s="50" t="inlineStr"/>
-      <c r="X76" s="50" t="inlineStr"/>
-      <c r="Y76" s="50" t="inlineStr"/>
-      <c r="Z76" s="51" t="inlineStr"/>
-      <c r="AA76" s="52" t="inlineStr"/>
-      <c r="AB76" s="53" t="inlineStr"/>
-      <c r="AC76" s="54" t="inlineStr"/>
-      <c r="AD76" s="54" t="inlineStr"/>
-      <c r="AE76" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 80 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF76" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG76" s="54" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="23" t="inlineStr"/>
-      <c r="B77" s="23" t="inlineStr"/>
-      <c r="C77" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D77" s="23" t="inlineStr"/>
-      <c r="E77" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F77" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G77" s="26" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H77" s="25" t="n">
-        <v>81</v>
-      </c>
-      <c r="I77" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J77" s="26" t="inlineStr"/>
-      <c r="K77" s="27" t="inlineStr"/>
-      <c r="L77" s="28" t="inlineStr"/>
-      <c r="M77" s="29" t="inlineStr"/>
-      <c r="N77" s="28" t="inlineStr"/>
-      <c r="O77" s="29" t="inlineStr"/>
-      <c r="P77" s="29" t="inlineStr"/>
-      <c r="Q77" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.81</t>
-        </is>
-      </c>
-      <c r="R77" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 81)</t>
-        </is>
-      </c>
-      <c r="S77" s="32" t="inlineStr"/>
-      <c r="T77" s="32" t="inlineStr"/>
-      <c r="U77" s="33" t="inlineStr"/>
-      <c r="V77" s="34" t="inlineStr"/>
-      <c r="W77" s="34" t="inlineStr"/>
-      <c r="X77" s="34" t="inlineStr"/>
-      <c r="Y77" s="34" t="inlineStr"/>
-      <c r="Z77" s="35" t="inlineStr"/>
-      <c r="AA77" s="36" t="inlineStr"/>
-      <c r="AB77" s="37" t="inlineStr"/>
-      <c r="AC77" s="38" t="inlineStr"/>
-      <c r="AD77" s="38" t="inlineStr"/>
-      <c r="AE77" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 81 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF77" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG77" s="38" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="39" t="inlineStr"/>
-      <c r="B78" s="39" t="inlineStr"/>
-      <c r="C78" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D78" s="39" t="inlineStr"/>
-      <c r="E78" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F78" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G78" s="42" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H78" s="41" t="n">
-        <v>82</v>
-      </c>
-      <c r="I78" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J78" s="42" t="inlineStr"/>
-      <c r="K78" s="43" t="inlineStr"/>
-      <c r="L78" s="44" t="inlineStr"/>
-      <c r="M78" s="45" t="inlineStr"/>
-      <c r="N78" s="44" t="inlineStr"/>
-      <c r="O78" s="45" t="inlineStr"/>
-      <c r="P78" s="45" t="inlineStr"/>
-      <c r="Q78" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.82</t>
-        </is>
-      </c>
-      <c r="R78" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 82)</t>
-        </is>
-      </c>
-      <c r="S78" s="48" t="inlineStr"/>
-      <c r="T78" s="48" t="inlineStr"/>
-      <c r="U78" s="49" t="inlineStr"/>
-      <c r="V78" s="50" t="inlineStr"/>
-      <c r="W78" s="50" t="inlineStr"/>
-      <c r="X78" s="50" t="inlineStr"/>
-      <c r="Y78" s="50" t="inlineStr"/>
-      <c r="Z78" s="51" t="inlineStr"/>
-      <c r="AA78" s="52" t="inlineStr"/>
-      <c r="AB78" s="53" t="inlineStr"/>
-      <c r="AC78" s="54" t="inlineStr"/>
-      <c r="AD78" s="54" t="inlineStr"/>
-      <c r="AE78" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 82 = 'spare (size 16)'</t>
-        </is>
-      </c>
-      <c r="AF78" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG78" s="54" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="23" t="inlineStr"/>
-      <c r="B79" s="23" t="inlineStr"/>
-      <c r="C79" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D79" s="23" t="inlineStr"/>
-      <c r="E79" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F79" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G79" s="26" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H79" s="25" t="n">
-        <v>97</v>
-      </c>
-      <c r="I79" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J79" s="26" t="inlineStr"/>
-      <c r="K79" s="27" t="inlineStr"/>
-      <c r="L79" s="28" t="inlineStr"/>
-      <c r="M79" s="29" t="inlineStr"/>
-      <c r="N79" s="28" t="inlineStr"/>
-      <c r="O79" s="29" t="inlineStr"/>
-      <c r="P79" s="29" t="inlineStr"/>
-      <c r="Q79" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.97</t>
-        </is>
-      </c>
-      <c r="R79" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 97)</t>
-        </is>
-      </c>
-      <c r="S79" s="32" t="inlineStr"/>
-      <c r="T79" s="32" t="inlineStr"/>
-      <c r="U79" s="33" t="inlineStr"/>
-      <c r="V79" s="34" t="inlineStr"/>
-      <c r="W79" s="34" t="inlineStr"/>
-      <c r="X79" s="34" t="inlineStr"/>
-      <c r="Y79" s="34" t="inlineStr"/>
-      <c r="Z79" s="35" t="inlineStr"/>
-      <c r="AA79" s="36" t="inlineStr"/>
-      <c r="AB79" s="37" t="inlineStr"/>
-      <c r="AC79" s="38" t="inlineStr"/>
-      <c r="AD79" s="38" t="inlineStr"/>
-      <c r="AE79" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 97 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF79" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG79" s="38" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="39" t="inlineStr"/>
-      <c r="B80" s="39" t="inlineStr"/>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D80" s="39" t="inlineStr"/>
-      <c r="E80" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F80" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G80" s="42" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H80" s="41" t="n">
-        <v>98</v>
-      </c>
-      <c r="I80" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J80" s="42" t="inlineStr"/>
-      <c r="K80" s="43" t="inlineStr"/>
-      <c r="L80" s="44" t="inlineStr"/>
-      <c r="M80" s="45" t="inlineStr"/>
-      <c r="N80" s="44" t="inlineStr"/>
-      <c r="O80" s="45" t="inlineStr"/>
-      <c r="P80" s="45" t="inlineStr"/>
-      <c r="Q80" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.98</t>
-        </is>
-      </c>
-      <c r="R80" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 98)</t>
-        </is>
-      </c>
-      <c r="S80" s="48" t="inlineStr"/>
-      <c r="T80" s="48" t="inlineStr"/>
-      <c r="U80" s="49" t="inlineStr"/>
-      <c r="V80" s="50" t="inlineStr"/>
-      <c r="W80" s="50" t="inlineStr"/>
-      <c r="X80" s="50" t="inlineStr"/>
-      <c r="Y80" s="50" t="inlineStr"/>
-      <c r="Z80" s="51" t="inlineStr"/>
-      <c r="AA80" s="52" t="inlineStr"/>
-      <c r="AB80" s="53" t="inlineStr"/>
-      <c r="AC80" s="54" t="inlineStr"/>
-      <c r="AD80" s="54" t="inlineStr"/>
-      <c r="AE80" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 98 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF80" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG80" s="54" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr"/>
-      <c r="B81" s="23" t="inlineStr"/>
-      <c r="C81" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D81" s="23" t="inlineStr"/>
-      <c r="E81" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F81" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G81" s="26" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H81" s="25" t="n">
-        <v>99</v>
-      </c>
-      <c r="I81" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J81" s="26" t="inlineStr"/>
-      <c r="K81" s="27" t="inlineStr"/>
-      <c r="L81" s="28" t="inlineStr"/>
-      <c r="M81" s="29" t="inlineStr"/>
-      <c r="N81" s="28" t="inlineStr"/>
-      <c r="O81" s="29" t="inlineStr"/>
-      <c r="P81" s="29" t="inlineStr"/>
-      <c r="Q81" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.99</t>
-        </is>
-      </c>
-      <c r="R81" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 99)</t>
-        </is>
-      </c>
-      <c r="S81" s="32" t="inlineStr"/>
-      <c r="T81" s="32" t="inlineStr"/>
-      <c r="U81" s="33" t="inlineStr"/>
-      <c r="V81" s="34" t="inlineStr"/>
-      <c r="W81" s="34" t="inlineStr"/>
-      <c r="X81" s="34" t="inlineStr"/>
-      <c r="Y81" s="34" t="inlineStr"/>
-      <c r="Z81" s="35" t="inlineStr"/>
-      <c r="AA81" s="36" t="inlineStr"/>
-      <c r="AB81" s="37" t="inlineStr"/>
-      <c r="AC81" s="38" t="inlineStr"/>
-      <c r="AD81" s="38" t="inlineStr"/>
-      <c r="AE81" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 99 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF81" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG81" s="38" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="39" t="inlineStr"/>
-      <c r="B82" s="39" t="inlineStr"/>
-      <c r="C82" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D82" s="39" t="inlineStr"/>
-      <c r="E82" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F82" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G82" s="42" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H82" s="41" t="n">
-        <v>100</v>
-      </c>
-      <c r="I82" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J82" s="42" t="inlineStr"/>
-      <c r="K82" s="43" t="inlineStr"/>
-      <c r="L82" s="44" t="inlineStr"/>
-      <c r="M82" s="45" t="inlineStr"/>
-      <c r="N82" s="44" t="inlineStr"/>
-      <c r="O82" s="45" t="inlineStr"/>
-      <c r="P82" s="45" t="inlineStr"/>
-      <c r="Q82" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.100</t>
-        </is>
-      </c>
-      <c r="R82" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 100)</t>
-        </is>
-      </c>
-      <c r="S82" s="48" t="inlineStr"/>
-      <c r="T82" s="48" t="inlineStr"/>
-      <c r="U82" s="49" t="inlineStr"/>
-      <c r="V82" s="50" t="inlineStr"/>
-      <c r="W82" s="50" t="inlineStr"/>
-      <c r="X82" s="50" t="inlineStr"/>
-      <c r="Y82" s="50" t="inlineStr"/>
-      <c r="Z82" s="51" t="inlineStr"/>
-      <c r="AA82" s="52" t="inlineStr"/>
-      <c r="AB82" s="53" t="inlineStr"/>
-      <c r="AC82" s="54" t="inlineStr"/>
-      <c r="AD82" s="54" t="inlineStr"/>
-      <c r="AE82" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 100 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF82" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG82" s="54" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="23" t="inlineStr"/>
-      <c r="B83" s="23" t="inlineStr"/>
-      <c r="C83" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D83" s="23" t="inlineStr"/>
-      <c r="E83" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F83" s="25" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G83" s="26" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H83" s="25" t="n">
-        <v>101</v>
-      </c>
-      <c r="I83" s="26" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J83" s="26" t="inlineStr"/>
-      <c r="K83" s="27" t="inlineStr"/>
-      <c r="L83" s="28" t="inlineStr"/>
-      <c r="M83" s="29" t="inlineStr"/>
-      <c r="N83" s="28" t="inlineStr"/>
-      <c r="O83" s="29" t="inlineStr"/>
-      <c r="P83" s="29" t="inlineStr"/>
-      <c r="Q83" s="30" t="inlineStr">
-        <is>
-          <t>DRB102.101</t>
-        </is>
-      </c>
-      <c r="R83" s="31" t="inlineStr">
-        <is>
-          <t>spare (DRB102 101)</t>
-        </is>
-      </c>
-      <c r="S83" s="32" t="inlineStr"/>
-      <c r="T83" s="32" t="inlineStr"/>
-      <c r="U83" s="33" t="inlineStr"/>
-      <c r="V83" s="34" t="inlineStr"/>
-      <c r="W83" s="34" t="inlineStr"/>
-      <c r="X83" s="34" t="inlineStr"/>
-      <c r="Y83" s="34" t="inlineStr"/>
-      <c r="Z83" s="35" t="inlineStr"/>
-      <c r="AA83" s="36" t="inlineStr"/>
-      <c r="AB83" s="37" t="inlineStr"/>
-      <c r="AC83" s="38" t="inlineStr"/>
-      <c r="AD83" s="38" t="inlineStr"/>
-      <c r="AE83" s="38" t="inlineStr">
-        <is>
-          <t>DRB102 101 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF83" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG83" s="38" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="39" t="inlineStr"/>
-      <c r="B84" s="39" t="inlineStr"/>
-      <c r="C84" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D84" s="39" t="inlineStr"/>
-      <c r="E84" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F84" s="41" t="inlineStr">
-        <is>
-          <t>bh_b_fw</t>
-        </is>
-      </c>
-      <c r="G84" s="42" t="inlineStr">
-        <is>
-          <t>BH-B (firewall bulkhead DRB102, RH)</t>
-        </is>
-      </c>
-      <c r="H84" s="41" t="n">
-        <v>102</v>
-      </c>
-      <c r="I84" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J84" s="42" t="inlineStr"/>
-      <c r="K84" s="43" t="inlineStr"/>
-      <c r="L84" s="44" t="inlineStr"/>
-      <c r="M84" s="45" t="inlineStr"/>
-      <c r="N84" s="44" t="inlineStr"/>
-      <c r="O84" s="45" t="inlineStr"/>
-      <c r="P84" s="45" t="inlineStr"/>
-      <c r="Q84" s="46" t="inlineStr">
-        <is>
-          <t>DRB102.102</t>
-        </is>
-      </c>
-      <c r="R84" s="47" t="inlineStr">
-        <is>
-          <t>spare (DRB102 102)</t>
-        </is>
-      </c>
-      <c r="S84" s="48" t="inlineStr"/>
-      <c r="T84" s="48" t="inlineStr"/>
-      <c r="U84" s="49" t="inlineStr"/>
-      <c r="V84" s="50" t="inlineStr"/>
-      <c r="W84" s="50" t="inlineStr"/>
-      <c r="X84" s="50" t="inlineStr"/>
-      <c r="Y84" s="50" t="inlineStr"/>
-      <c r="Z84" s="51" t="inlineStr"/>
-      <c r="AA84" s="52" t="inlineStr"/>
-      <c r="AB84" s="53" t="inlineStr"/>
-      <c r="AC84" s="54" t="inlineStr"/>
-      <c r="AD84" s="54" t="inlineStr"/>
-      <c r="AE84" s="54" t="inlineStr">
-        <is>
-          <t>DRB102 102 = 'spare (size 12)'</t>
-        </is>
-      </c>
-      <c r="AF84" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG84" s="54" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="23" t="inlineStr"/>
-      <c r="B85" s="23" t="inlineStr"/>
-      <c r="C85" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D85" s="23" t="inlineStr"/>
-      <c r="E85" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F85" s="25" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="G85" s="26" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H85" s="25" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="I85" s="26" t="inlineStr">
-        <is>
-          <t>spare, not used</t>
-        </is>
-      </c>
-      <c r="J85" s="26" t="inlineStr"/>
-      <c r="K85" s="27" t="inlineStr"/>
-      <c r="L85" s="28" t="inlineStr"/>
-      <c r="M85" s="29" t="inlineStr"/>
-      <c r="N85" s="28" t="inlineStr"/>
-      <c r="O85" s="29" t="inlineStr"/>
-      <c r="P85" s="29" t="inlineStr"/>
-      <c r="Q85" s="30" t="inlineStr">
-        <is>
-          <t>ECU-B.B1</t>
-        </is>
-      </c>
-      <c r="R85" s="31" t="inlineStr">
-        <is>
-          <t>spare (ECU-B B1)</t>
-        </is>
-      </c>
-      <c r="S85" s="32" t="inlineStr"/>
-      <c r="T85" s="32" t="inlineStr"/>
-      <c r="U85" s="33" t="inlineStr"/>
-      <c r="V85" s="34" t="inlineStr"/>
-      <c r="W85" s="34" t="inlineStr"/>
-      <c r="X85" s="34" t="inlineStr"/>
-      <c r="Y85" s="34" t="inlineStr"/>
-      <c r="Z85" s="35" t="inlineStr"/>
-      <c r="AA85" s="36" t="inlineStr"/>
-      <c r="AB85" s="37" t="inlineStr"/>
-      <c r="AC85" s="38" t="inlineStr"/>
-      <c r="AD85" s="38" t="inlineStr"/>
-      <c r="AE85" s="38" t="inlineStr"/>
-      <c r="AF85" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG85" s="38" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="39" t="inlineStr"/>
-      <c r="B86" s="39" t="inlineStr"/>
-      <c r="C86" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D86" s="39" t="inlineStr"/>
-      <c r="E86" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F86" s="41" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="G86" s="42" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H86" s="41" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="I86" s="42" t="inlineStr">
-        <is>
-          <t>spare, not used</t>
-        </is>
-      </c>
-      <c r="J86" s="42" t="inlineStr"/>
-      <c r="K86" s="43" t="inlineStr"/>
-      <c r="L86" s="44" t="inlineStr"/>
-      <c r="M86" s="45" t="inlineStr"/>
-      <c r="N86" s="44" t="inlineStr"/>
-      <c r="O86" s="45" t="inlineStr"/>
-      <c r="P86" s="45" t="inlineStr"/>
-      <c r="Q86" s="46" t="inlineStr">
-        <is>
-          <t>ECU-B.B2</t>
-        </is>
-      </c>
-      <c r="R86" s="47" t="inlineStr">
-        <is>
-          <t>spare (ECU-B B2)</t>
-        </is>
-      </c>
-      <c r="S86" s="48" t="inlineStr"/>
-      <c r="T86" s="48" t="inlineStr"/>
-      <c r="U86" s="49" t="inlineStr"/>
-      <c r="V86" s="50" t="inlineStr"/>
-      <c r="W86" s="50" t="inlineStr"/>
-      <c r="X86" s="50" t="inlineStr"/>
-      <c r="Y86" s="50" t="inlineStr"/>
-      <c r="Z86" s="51" t="inlineStr"/>
-      <c r="AA86" s="52" t="inlineStr"/>
-      <c r="AB86" s="53" t="inlineStr"/>
-      <c r="AC86" s="54" t="inlineStr"/>
-      <c r="AD86" s="54" t="inlineStr"/>
-      <c r="AE86" s="54" t="inlineStr"/>
-      <c r="AF86" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG86" s="54" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="23" t="inlineStr"/>
-      <c r="B87" s="23" t="inlineStr"/>
-      <c r="C87" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D87" s="23" t="inlineStr"/>
-      <c r="E87" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F87" s="25" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="G87" s="26" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H87" s="25" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="I87" s="26" t="inlineStr">
-        <is>
-          <t>spare, not used</t>
-        </is>
-      </c>
-      <c r="J87" s="26" t="inlineStr"/>
-      <c r="K87" s="27" t="inlineStr"/>
-      <c r="L87" s="28" t="inlineStr"/>
-      <c r="M87" s="29" t="inlineStr"/>
-      <c r="N87" s="28" t="inlineStr"/>
-      <c r="O87" s="29" t="inlineStr"/>
-      <c r="P87" s="29" t="inlineStr"/>
-      <c r="Q87" s="30" t="inlineStr">
-        <is>
-          <t>ECU-B.B3</t>
-        </is>
-      </c>
-      <c r="R87" s="31" t="inlineStr">
-        <is>
-          <t>spare (ECU-B B3)</t>
-        </is>
-      </c>
-      <c r="S87" s="32" t="inlineStr"/>
-      <c r="T87" s="32" t="inlineStr"/>
-      <c r="U87" s="33" t="inlineStr"/>
-      <c r="V87" s="34" t="inlineStr"/>
-      <c r="W87" s="34" t="inlineStr"/>
-      <c r="X87" s="34" t="inlineStr"/>
-      <c r="Y87" s="34" t="inlineStr"/>
-      <c r="Z87" s="35" t="inlineStr"/>
-      <c r="AA87" s="36" t="inlineStr"/>
-      <c r="AB87" s="37" t="inlineStr"/>
-      <c r="AC87" s="38" t="inlineStr"/>
-      <c r="AD87" s="38" t="inlineStr"/>
-      <c r="AE87" s="38" t="inlineStr"/>
-      <c r="AF87" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG87" s="38" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="39" t="inlineStr"/>
-      <c r="B88" s="39" t="inlineStr"/>
-      <c r="C88" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D88" s="39" t="inlineStr"/>
-      <c r="E88" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F88" s="41" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="G88" s="42" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H88" s="41" t="inlineStr">
-        <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="I88" s="42" t="inlineStr">
-        <is>
-          <t>spare, not used</t>
-        </is>
-      </c>
-      <c r="J88" s="42" t="inlineStr"/>
-      <c r="K88" s="43" t="inlineStr"/>
-      <c r="L88" s="44" t="inlineStr"/>
-      <c r="M88" s="45" t="inlineStr"/>
-      <c r="N88" s="44" t="inlineStr"/>
-      <c r="O88" s="45" t="inlineStr"/>
-      <c r="P88" s="45" t="inlineStr"/>
-      <c r="Q88" s="46" t="inlineStr">
-        <is>
-          <t>ECU-B.B4</t>
-        </is>
-      </c>
-      <c r="R88" s="47" t="inlineStr">
-        <is>
-          <t>spare (ECU-B B4)</t>
-        </is>
-      </c>
-      <c r="S88" s="48" t="inlineStr"/>
-      <c r="T88" s="48" t="inlineStr"/>
-      <c r="U88" s="49" t="inlineStr"/>
-      <c r="V88" s="50" t="inlineStr"/>
-      <c r="W88" s="50" t="inlineStr"/>
-      <c r="X88" s="50" t="inlineStr"/>
-      <c r="Y88" s="50" t="inlineStr"/>
-      <c r="Z88" s="51" t="inlineStr"/>
-      <c r="AA88" s="52" t="inlineStr"/>
-      <c r="AB88" s="53" t="inlineStr"/>
-      <c r="AC88" s="54" t="inlineStr"/>
-      <c r="AD88" s="54" t="inlineStr"/>
-      <c r="AE88" s="54" t="inlineStr"/>
-      <c r="AF88" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG88" s="54" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="23" t="inlineStr"/>
-      <c r="B89" s="23" t="inlineStr"/>
-      <c r="C89" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D89" s="23" t="inlineStr"/>
-      <c r="E89" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F89" s="25" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="G89" s="26" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H89" s="25" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="I89" s="26" t="inlineStr">
-        <is>
-          <t>spare, not used</t>
-        </is>
-      </c>
-      <c r="J89" s="26" t="inlineStr"/>
-      <c r="K89" s="27" t="inlineStr"/>
-      <c r="L89" s="28" t="inlineStr"/>
-      <c r="M89" s="29" t="inlineStr"/>
-      <c r="N89" s="28" t="inlineStr"/>
-      <c r="O89" s="29" t="inlineStr"/>
-      <c r="P89" s="29" t="inlineStr"/>
-      <c r="Q89" s="30" t="inlineStr">
-        <is>
-          <t>ECU-B.B8</t>
-        </is>
-      </c>
-      <c r="R89" s="31" t="inlineStr">
-        <is>
-          <t>spare (ECU-B B8)</t>
-        </is>
-      </c>
-      <c r="S89" s="32" t="inlineStr"/>
-      <c r="T89" s="32" t="inlineStr"/>
-      <c r="U89" s="33" t="inlineStr"/>
-      <c r="V89" s="34" t="inlineStr"/>
-      <c r="W89" s="34" t="inlineStr"/>
-      <c r="X89" s="34" t="inlineStr"/>
-      <c r="Y89" s="34" t="inlineStr"/>
-      <c r="Z89" s="35" t="inlineStr"/>
-      <c r="AA89" s="36" t="inlineStr"/>
-      <c r="AB89" s="37" t="inlineStr"/>
-      <c r="AC89" s="38" t="inlineStr"/>
-      <c r="AD89" s="38" t="inlineStr"/>
-      <c r="AE89" s="38" t="inlineStr"/>
-      <c r="AF89" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG89" s="38" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="39" t="inlineStr"/>
-      <c r="B90" s="39" t="inlineStr"/>
-      <c r="C90" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D90" s="39" t="inlineStr"/>
-      <c r="E90" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F90" s="41" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="G90" s="42" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H90" s="41" t="inlineStr">
-        <is>
-          <t>B11</t>
-        </is>
-      </c>
-      <c r="I90" s="42" t="inlineStr">
-        <is>
-          <t>spare, not used</t>
-        </is>
-      </c>
-      <c r="J90" s="42" t="inlineStr"/>
-      <c r="K90" s="43" t="inlineStr"/>
-      <c r="L90" s="44" t="inlineStr"/>
-      <c r="M90" s="45" t="inlineStr"/>
-      <c r="N90" s="44" t="inlineStr"/>
-      <c r="O90" s="45" t="inlineStr"/>
-      <c r="P90" s="45" t="inlineStr"/>
-      <c r="Q90" s="46" t="inlineStr">
-        <is>
-          <t>ECU-B.B11</t>
-        </is>
-      </c>
-      <c r="R90" s="47" t="inlineStr">
-        <is>
-          <t>spare (ECU-B B11)</t>
-        </is>
-      </c>
-      <c r="S90" s="48" t="inlineStr"/>
-      <c r="T90" s="48" t="inlineStr"/>
-      <c r="U90" s="49" t="inlineStr"/>
-      <c r="V90" s="50" t="inlineStr"/>
-      <c r="W90" s="50" t="inlineStr"/>
-      <c r="X90" s="50" t="inlineStr"/>
-      <c r="Y90" s="50" t="inlineStr"/>
-      <c r="Z90" s="51" t="inlineStr"/>
-      <c r="AA90" s="52" t="inlineStr"/>
-      <c r="AB90" s="53" t="inlineStr"/>
-      <c r="AC90" s="54" t="inlineStr"/>
-      <c r="AD90" s="54" t="inlineStr"/>
-      <c r="AE90" s="54" t="inlineStr"/>
-      <c r="AF90" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG90" s="54" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="23" t="inlineStr"/>
-      <c r="B91" s="23" t="inlineStr"/>
-      <c r="C91" s="23" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D91" s="23" t="inlineStr"/>
-      <c r="E91" s="24" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F91" s="25" t="inlineStr">
-        <is>
-          <t>ecu_b</t>
-        </is>
-      </c>
-      <c r="G91" s="26" t="inlineStr">
-        <is>
-          <t>ECU-B (Link G4X plug B, centre dash)</t>
-        </is>
-      </c>
-      <c r="H91" s="25" t="inlineStr">
-        <is>
-          <t>B14</t>
-        </is>
-      </c>
-      <c r="I91" s="26" t="inlineStr">
-        <is>
-          <t>spare, not used</t>
-        </is>
-      </c>
-      <c r="J91" s="26" t="inlineStr"/>
-      <c r="K91" s="27" t="inlineStr"/>
-      <c r="L91" s="28" t="inlineStr"/>
-      <c r="M91" s="29" t="inlineStr"/>
-      <c r="N91" s="28" t="inlineStr"/>
-      <c r="O91" s="29" t="inlineStr"/>
-      <c r="P91" s="29" t="inlineStr"/>
-      <c r="Q91" s="30" t="inlineStr">
-        <is>
-          <t>ECU-B.B14</t>
-        </is>
-      </c>
-      <c r="R91" s="31" t="inlineStr">
-        <is>
-          <t>spare (ECU-B B14)</t>
-        </is>
-      </c>
-      <c r="S91" s="32" t="inlineStr"/>
-      <c r="T91" s="32" t="inlineStr"/>
-      <c r="U91" s="33" t="inlineStr"/>
-      <c r="V91" s="34" t="inlineStr"/>
-      <c r="W91" s="34" t="inlineStr"/>
-      <c r="X91" s="34" t="inlineStr"/>
-      <c r="Y91" s="34" t="inlineStr"/>
-      <c r="Z91" s="35" t="inlineStr"/>
-      <c r="AA91" s="36" t="inlineStr"/>
-      <c r="AB91" s="37" t="inlineStr"/>
-      <c r="AC91" s="38" t="inlineStr"/>
-      <c r="AD91" s="38" t="inlineStr"/>
-      <c r="AE91" s="38" t="inlineStr"/>
-      <c r="AF91" s="38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG91" s="38" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="39" t="inlineStr"/>
-      <c r="B92" s="39" t="inlineStr"/>
-      <c r="C92" s="39" t="inlineStr">
-        <is>
-          <t>B-cabin</t>
-        </is>
-      </c>
-      <c r="D92" s="39" t="inlineStr"/>
-      <c r="E92" s="40" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="F92" s="41" t="inlineStr">
-        <is>
-          <t>ix_ws_rear_p</t>
-        </is>
-      </c>
-      <c r="G92" s="42" t="inlineStr">
-        <is>
-          <t>IX-WS-R inline to rear VRC (dash above ECU)</t>
-        </is>
-      </c>
-      <c r="H92" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="I92" s="42" t="inlineStr">
-        <is>
-          <t>spare, sealing plug</t>
-        </is>
-      </c>
-      <c r="J92" s="42" t="inlineStr"/>
-      <c r="K92" s="43" t="inlineStr"/>
-      <c r="L92" s="44" t="inlineStr"/>
-      <c r="M92" s="45" t="inlineStr"/>
-      <c r="N92" s="44" t="inlineStr"/>
-      <c r="O92" s="45" t="inlineStr"/>
-      <c r="P92" s="45" t="inlineStr"/>
-      <c r="Q92" s="46" t="inlineStr">
-        <is>
-          <t>ix_ws_rear_p.6</t>
-        </is>
-      </c>
-      <c r="R92" s="47" t="inlineStr">
-        <is>
-          <t>spare (ix_ws_rear_p 6)</t>
-        </is>
-      </c>
-      <c r="S92" s="48" t="inlineStr"/>
-      <c r="T92" s="48" t="inlineStr"/>
-      <c r="U92" s="49" t="inlineStr"/>
-      <c r="V92" s="50" t="inlineStr"/>
-      <c r="W92" s="50" t="inlineStr"/>
-      <c r="X92" s="50" t="inlineStr"/>
-      <c r="Y92" s="50" t="inlineStr"/>
-      <c r="Z92" s="51" t="inlineStr"/>
-      <c r="AA92" s="52" t="inlineStr"/>
-      <c r="AB92" s="53" t="inlineStr"/>
-      <c r="AC92" s="54" t="inlineStr"/>
-      <c r="AD92" s="54" t="inlineStr"/>
-      <c r="AE92" s="54" t="inlineStr"/>
-      <c r="AF92" s="54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="AG92" s="54" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:AG92"/>
+  <autoFilter ref="A2:AG72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -10355,12 +8895,12 @@
       </c>
       <c r="D8" s="46" t="inlineStr">
         <is>
-          <t>DRB102.76</t>
+          <t>DRB102.78</t>
         </is>
       </c>
       <c r="E8" s="47" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out (DRB102 76)</t>
+          <t>Reverse sw +12 V out (DRB102 78)</t>
         </is>
       </c>
       <c r="F8" s="48" t="n">
@@ -10691,7 +9231,7 @@
       </c>
       <c r="G3" s="36" t="inlineStr">
         <is>
-          <t>shared DRB102 (section B here, section A on A-cabin)</t>
+          <t>shared DRB102 (loom B wires here, loom A wires on A-cabin)</t>
         </is>
       </c>
     </row>
@@ -10936,7 +9476,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D3" s="26" t="inlineStr">
         <is>
@@ -10954,7 +9494,7 @@
         </is>
       </c>
       <c r="G3" s="28" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="H3" s="29" t="inlineStr">
         <is>
@@ -11032,7 +9572,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
@@ -11050,7 +9590,7 @@
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
@@ -11059,7 +9599,7 @@
       </c>
       <c r="I5" s="59" t="inlineStr">
         <is>
-          <t>Reverse sw +12 V out (DRB102 76)</t>
+          <t>Reverse sw +12 V out (DRB102 78)</t>
         </is>
       </c>
       <c r="J5" s="60" t="inlineStr">
@@ -11080,7 +9620,7 @@
         </is>
       </c>
       <c r="C6" s="41" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D6" s="42" t="inlineStr">
         <is>
@@ -11098,7 +9638,7 @@
         </is>
       </c>
       <c r="G6" s="44" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H6" s="45" t="inlineStr">
         <is>
@@ -11128,7 +9668,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D7" s="26" t="inlineStr">
         <is>
@@ -11146,7 +9686,7 @@
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
@@ -11176,7 +9716,7 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="D8" s="42" t="inlineStr">
         <is>
@@ -11194,7 +9734,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="H8" s="45" t="inlineStr">
         <is>
@@ -11224,7 +9764,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D9" s="26" t="inlineStr">
         <is>
@@ -11242,7 +9782,7 @@
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
@@ -11272,7 +9812,7 @@
         </is>
       </c>
       <c r="C10" s="41" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D10" s="42" t="inlineStr">
         <is>
@@ -11290,7 +9830,7 @@
         </is>
       </c>
       <c r="G10" s="44" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H10" s="45" t="inlineStr">
         <is>
@@ -11320,7 +9860,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D11" s="26" t="inlineStr">
         <is>
@@ -11338,7 +9878,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
@@ -11368,7 +9908,7 @@
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="D12" s="42" t="inlineStr">
         <is>
@@ -11386,7 +9926,7 @@
         </is>
       </c>
       <c r="G12" s="44" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="H12" s="45" t="inlineStr">
         <is>
@@ -11416,7 +9956,7 @@
         </is>
       </c>
       <c r="C13" s="25" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D13" s="26" t="inlineStr">
         <is>
@@ -11434,7 +9974,7 @@
         </is>
       </c>
       <c r="G13" s="28" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
@@ -11464,7 +10004,7 @@
         </is>
       </c>
       <c r="C14" s="41" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="D14" s="42" t="inlineStr">
         <is>
@@ -11482,7 +10022,7 @@
         </is>
       </c>
       <c r="G14" s="44" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
@@ -11512,7 +10052,7 @@
         </is>
       </c>
       <c r="C15" s="25" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
@@ -11530,7 +10070,7 @@
         </is>
       </c>
       <c r="G15" s="28" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
@@ -11560,7 +10100,7 @@
         </is>
       </c>
       <c r="C16" s="41" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D16" s="42" t="inlineStr">
         <is>
@@ -11578,7 +10118,7 @@
         </is>
       </c>
       <c r="G16" s="44" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="H16" s="45" t="inlineStr">
         <is>
@@ -11608,7 +10148,7 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
@@ -11626,7 +10166,7 @@
         </is>
       </c>
       <c r="G17" s="28" t="n">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
@@ -11656,7 +10196,7 @@
         </is>
       </c>
       <c r="C18" s="41" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="D18" s="42" t="inlineStr">
         <is>
@@ -11674,7 +10214,7 @@
         </is>
       </c>
       <c r="G18" s="44" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="H18" s="45" t="inlineStr">
         <is>
@@ -11704,7 +10244,7 @@
         </is>
       </c>
       <c r="C19" s="25" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
@@ -11722,7 +10262,7 @@
         </is>
       </c>
       <c r="G19" s="28" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
@@ -11752,7 +10292,7 @@
         </is>
       </c>
       <c r="C20" s="41" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D20" s="42" t="inlineStr">
         <is>
@@ -11770,7 +10310,7 @@
         </is>
       </c>
       <c r="G20" s="44" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H20" s="45" t="inlineStr">
         <is>
@@ -11800,7 +10340,7 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
@@ -11818,7 +10358,7 @@
         </is>
       </c>
       <c r="G21" s="28" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
@@ -11848,7 +10388,7 @@
         </is>
       </c>
       <c r="C22" s="41" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="D22" s="42" t="inlineStr">
         <is>
@@ -11866,7 +10406,7 @@
         </is>
       </c>
       <c r="G22" s="44" t="n">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="H22" s="45" t="inlineStr">
         <is>
@@ -11896,7 +10436,7 @@
         </is>
       </c>
       <c r="C23" s="25" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
@@ -11914,7 +10454,7 @@
         </is>
       </c>
       <c r="G23" s="28" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H23" s="29" t="inlineStr">
         <is>
@@ -11923,7 +10463,7 @@
       </c>
       <c r="I23" s="59" t="inlineStr">
         <is>
-          <t>Back-up sw +12 V in (DRB102 62)</t>
+          <t>Back-up sw +12 V in (DRB102 77)</t>
         </is>
       </c>
       <c r="J23" s="60" t="inlineStr">
@@ -11944,7 +10484,7 @@
         </is>
       </c>
       <c r="C24" s="41" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="D24" s="42" t="inlineStr">
         <is>
@@ -11962,7 +10502,7 @@
         </is>
       </c>
       <c r="G24" s="44" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H24" s="45" t="inlineStr">
         <is>

--- a/docs/harness/wirelist/B-cabin-wirelist.xlsx
+++ b/docs/harness/wirelist/B-cabin-wirelist.xlsx
@@ -1201,14 +1201,10 @@
       </c>
       <c r="V3" s="34" t="inlineStr">
         <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="W3" s="34" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W3" s="34" t="inlineStr"/>
       <c r="X3" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -1316,14 +1312,10 @@
       </c>
       <c r="V4" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W4" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W4" s="50" t="inlineStr"/>
       <c r="X4" s="50" t="inlineStr">
         <is>
           <t>Blue-Yellow-White</t>
@@ -1431,14 +1423,10 @@
       </c>
       <c r="V5" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W5" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W5" s="34" t="inlineStr"/>
       <c r="X5" s="34" t="inlineStr">
         <is>
           <t>Blue-Yellow-White</t>
@@ -1546,14 +1534,10 @@
       </c>
       <c r="V6" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W6" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W6" s="50" t="inlineStr"/>
       <c r="X6" s="50" t="inlineStr">
         <is>
           <t>Blue-Yellow</t>
@@ -1661,7 +1645,7 @@
       </c>
       <c r="V7" s="34" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W7" s="34" t="inlineStr"/>
@@ -1774,14 +1758,10 @@
       </c>
       <c r="V8" s="50" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W8" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W8" s="50" t="inlineStr"/>
       <c r="X8" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow</t>
@@ -1889,7 +1869,7 @@
       </c>
       <c r="V9" s="34" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W9" s="34" t="inlineStr"/>
@@ -2002,7 +1982,7 @@
       </c>
       <c r="V10" s="50" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W10" s="50" t="inlineStr"/>
@@ -2115,7 +2095,7 @@
       </c>
       <c r="V11" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W11" s="34" t="inlineStr"/>
@@ -2232,7 +2212,7 @@
       </c>
       <c r="V12" s="50" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W12" s="50" t="inlineStr"/>
@@ -2351,7 +2331,7 @@
       </c>
       <c r="V13" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W13" s="34" t="inlineStr"/>
@@ -2809,14 +2789,10 @@
       </c>
       <c r="V17" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W17" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W17" s="34" t="inlineStr"/>
       <c r="X17" s="34" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -3152,7 +3128,7 @@
       </c>
       <c r="V20" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W20" s="50" t="inlineStr"/>
@@ -3265,7 +3241,7 @@
       </c>
       <c r="V21" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W21" s="34" t="inlineStr"/>
@@ -3382,7 +3358,7 @@
       </c>
       <c r="V22" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W22" s="50" t="inlineStr"/>
@@ -3610,14 +3586,10 @@
       </c>
       <c r="V24" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W24" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W24" s="50" t="inlineStr"/>
       <c r="X24" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -4439,7 +4411,7 @@
       </c>
       <c r="V31" s="34" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W31" s="34" t="inlineStr"/>
@@ -4556,7 +4528,7 @@
       </c>
       <c r="V32" s="50" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W32" s="50" t="inlineStr"/>
@@ -4685,7 +4657,7 @@
       </c>
       <c r="V33" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W33" s="34" t="inlineStr"/>
@@ -4796,14 +4768,10 @@
       </c>
       <c r="V34" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W34" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W34" s="50" t="inlineStr"/>
       <c r="X34" s="50" t="inlineStr">
         <is>
           <t>Blue-Blue-Yellow</t>
@@ -5133,7 +5101,7 @@
       </c>
       <c r="V37" s="34" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W37" s="34" t="inlineStr"/>
@@ -5494,7 +5462,7 @@
       </c>
       <c r="V40" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W40" s="50" t="inlineStr"/>
@@ -5829,14 +5797,10 @@
       </c>
       <c r="V43" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W43" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W43" s="34" t="inlineStr"/>
       <c r="X43" s="34" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -5944,14 +5908,10 @@
       </c>
       <c r="V44" s="50" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W44" s="50" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W44" s="50" t="inlineStr"/>
       <c r="X44" s="50" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -6057,14 +6017,10 @@
       </c>
       <c r="V45" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W45" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W45" s="34" t="inlineStr"/>
       <c r="X45" s="34" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -6179,11 +6135,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W46" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W46" s="50" t="inlineStr"/>
       <c r="X46" s="50" t="inlineStr">
         <is>
           <t>White</t>
@@ -6304,11 +6256,7 @@
           <t>Red</t>
         </is>
       </c>
-      <c r="W47" s="34" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+      <c r="W47" s="34" t="inlineStr"/>
       <c r="X47" s="34" t="inlineStr">
         <is>
           <t>White</t>
@@ -6426,14 +6374,10 @@
       </c>
       <c r="V48" s="50" t="inlineStr">
         <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="W48" s="50" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="W48" s="50" t="inlineStr"/>
       <c r="X48" s="50" t="inlineStr">
         <is>
           <t>White</t>
@@ -6547,14 +6491,10 @@
       </c>
       <c r="V49" s="34" t="inlineStr">
         <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="W49" s="34" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="W49" s="34" t="inlineStr"/>
       <c r="X49" s="34" t="inlineStr">
         <is>
           <t>White-Yellow-Blue</t>
@@ -6663,11 +6603,7 @@
           <t>Black</t>
         </is>
       </c>
-      <c r="W50" s="50" t="inlineStr">
-        <is>
-          <t>Blue</t>
-        </is>
-      </c>
+      <c r="W50" s="50" t="inlineStr"/>
       <c r="X50" s="50" t="inlineStr">
         <is>
           <t>White-Yellow-Blue</t>
@@ -6898,7 +6834,7 @@
       </c>
       <c r="V52" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="W52" s="50" t="inlineStr"/>
@@ -7007,14 +6943,10 @@
       </c>
       <c r="V53" s="34" t="inlineStr">
         <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="W53" s="34" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="W53" s="34" t="inlineStr"/>
       <c r="X53" s="34" t="inlineStr">
         <is>
           <t>Yellow-Yellow-Blue</t>
@@ -7120,7 +7052,7 @@
       </c>
       <c r="V54" s="50" t="inlineStr">
         <is>
-          <t>Gray</t>
+          <t>White</t>
         </is>
       </c>
       <c r="W54" s="50" t="inlineStr"/>
